--- a/excel-calculation/excel-model/S&R_position.xlsx
+++ b/excel-calculation/excel-model/S&R_position.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WiN\Desktop\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SaaS Project\trading-alerts-saas-public\excel-calculation\excel-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACA98C1-E47B-41F4-806E-952B7D892C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAFD5CCE-16E1-4F95-8BD8-92905362F251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-7992" yWindow="1596" windowWidth="15306" windowHeight="8952" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="S&amp;R Position" sheetId="4" r:id="rId1"/>
@@ -352,24 +352,6 @@
     <t>Close</t>
   </si>
   <si>
-    <t>Peak_Line_1</t>
-  </si>
-  <si>
-    <t>Peak_Line_2</t>
-  </si>
-  <si>
-    <t>Peak_Line_3</t>
-  </si>
-  <si>
-    <t>Bottom_Line_1</t>
-  </si>
-  <si>
-    <t>Bottom_Line_2</t>
-  </si>
-  <si>
-    <t>Bottom_Line_3</t>
-  </si>
-  <si>
     <t>Status_Peak_Line_1</t>
   </si>
   <si>
@@ -388,10 +370,28 @@
     <t>Status_Bottom_Line_3</t>
   </si>
   <si>
-    <t>Count_R</t>
-  </si>
-  <si>
-    <t>Count_S</t>
+    <t>horiz_peak_line_1</t>
+  </si>
+  <si>
+    <t>horiz_peak_line_2</t>
+  </si>
+  <si>
+    <t>horiz_peak_line_3</t>
+  </si>
+  <si>
+    <t>horiz_bottom_line_1</t>
+  </si>
+  <si>
+    <t>horiz_bottom_line_2</t>
+  </si>
+  <si>
+    <t>horiz_bottom_line_3</t>
+  </si>
+  <si>
+    <t>res_count</t>
+  </si>
+  <si>
+    <t>sup_count</t>
   </si>
 </sst>
 </file>
@@ -544,7 +544,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -739,12 +739,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -944,7 +938,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1035,7 +1031,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'S&amp;R Position'!$E$4</c:f>
+              <c:f>'S&amp;R Position'!$E$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1058,7 +1054,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'S&amp;R Position'!$E$5:$E$103</c:f>
+              <c:f>'S&amp;R Position'!$E$3:$E$101</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="99"/>
@@ -1374,11 +1370,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'S&amp;R Position'!$F$4</c:f>
+              <c:f>'S&amp;R Position'!$F$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Peak_Line_1</c:v>
+                  <c:v>horiz_peak_line_1</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1397,7 +1393,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'S&amp;R Position'!$F$5:$F$103</c:f>
+              <c:f>'S&amp;R Position'!$F$3:$F$101</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="99"/>
@@ -1713,11 +1709,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'S&amp;R Position'!$G$4</c:f>
+              <c:f>'S&amp;R Position'!$G$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Peak_Line_2</c:v>
+                  <c:v>horiz_peak_line_2</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1736,7 +1732,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'S&amp;R Position'!$G$5:$G$103</c:f>
+              <c:f>'S&amp;R Position'!$G$3:$G$101</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="99"/>
@@ -2052,11 +2048,11 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>'S&amp;R Position'!$H$4</c:f>
+              <c:f>'S&amp;R Position'!$H$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Peak_Line_3</c:v>
+                  <c:v>horiz_peak_line_3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2075,7 +2071,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'S&amp;R Position'!$H$5:$H$103</c:f>
+              <c:f>'S&amp;R Position'!$H$3:$H$101</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="99"/>
@@ -2391,11 +2387,11 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>'S&amp;R Position'!$I$4</c:f>
+              <c:f>'S&amp;R Position'!$I$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Bottom_Line_1</c:v>
+                  <c:v>horiz_bottom_line_1</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2414,7 +2410,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'S&amp;R Position'!$I$5:$I$103</c:f>
+              <c:f>'S&amp;R Position'!$I$3:$I$101</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="99"/>
@@ -2730,11 +2726,11 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>'S&amp;R Position'!$J$4</c:f>
+              <c:f>'S&amp;R Position'!$J$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Bottom_Line_2</c:v>
+                  <c:v>horiz_bottom_line_2</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2753,7 +2749,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'S&amp;R Position'!$J$5:$J$103</c:f>
+              <c:f>'S&amp;R Position'!$J$3:$J$101</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="99"/>
@@ -3069,11 +3065,11 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>'S&amp;R Position'!$K$4</c:f>
+              <c:f>'S&amp;R Position'!$K$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Bottom_Line_3</c:v>
+                  <c:v>horiz_bottom_line_3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3094,7 +3090,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'S&amp;R Position'!$K$5:$K$103</c:f>
+              <c:f>'S&amp;R Position'!$K$3:$K$101</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="99"/>
@@ -4178,13 +4174,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>106</xdr:row>
+      <xdr:row>104</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>657225</xdr:colOff>
-      <xdr:row>156</xdr:row>
+      <xdr:row>154</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4534,7 +4530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D2B11ED-ADA3-4BD7-B8BE-0DF761DB1DBE}">
-  <dimension ref="A3:U103"/>
+  <dimension ref="A2:T101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="3.15625" bestFit="1" customWidth="1"/>
@@ -4549,89 +4545,214 @@
     <col min="16" max="16" width="11.1015625" customWidth="1"/>
     <col min="17" max="17" width="10.41796875" customWidth="1"/>
     <col min="18" max="18" width="10.3125" customWidth="1"/>
-    <col min="19" max="19" width="4.26171875" customWidth="1"/>
-    <col min="20" max="20" width="7.7890625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="19.734375" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="19.83984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.83984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.26171875" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="19.734375" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="19.83984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+    <row r="2" spans="1:20" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="L2" s="11"/>
+      <c r="M2" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>119</v>
+      </c>
     </row>
-    <row r="4" spans="1:21" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C4" s="10" t="s">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3">
+        <v>153.249</v>
+      </c>
+      <c r="F3">
+        <v>153.03800000000001</v>
+      </c>
+      <c r="G3">
+        <v>152.911</v>
+      </c>
+      <c r="H3">
+        <v>153.27099999999999</v>
+      </c>
+      <c r="I3">
+        <v>152.56</v>
+      </c>
+      <c r="J3">
+        <v>152.60300000000001</v>
+      </c>
+      <c r="K3">
+        <v>152.768</v>
+      </c>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1" t="str">
+        <f t="shared" ref="M3:M34" si="0">IF($E3&gt;F3,"SUP","RES")</f>
+        <v>SUP</v>
+      </c>
+      <c r="N3" s="1" t="str">
+        <f t="shared" ref="N3:N34" si="1">IF($E3&gt;G3,"SUP","RES")</f>
+        <v>SUP</v>
+      </c>
+      <c r="O3" s="1" t="str">
+        <f t="shared" ref="O3:O34" si="2">IF($E3&gt;H3,"SUP","RES")</f>
+        <v>RES</v>
+      </c>
+      <c r="P3" s="1" t="str">
+        <f t="shared" ref="P3:P34" si="3">IF($E3&gt;I3,"SUP","RES")</f>
+        <v>SUP</v>
+      </c>
+      <c r="Q3" s="1" t="str">
+        <f t="shared" ref="Q3:Q34" si="4">IF($E3&gt;J3,"SUP","RES")</f>
+        <v>SUP</v>
+      </c>
+      <c r="R3" s="1" t="str">
+        <f t="shared" ref="R3:R34" si="5">IF($E3&gt;K3,"SUP","RES")</f>
+        <v>SUP</v>
+      </c>
+      <c r="S3" s="2">
+        <f t="shared" ref="S3:S34" si="6">COUNTIF(M3:R3,"RES")</f>
+        <v>1</v>
+      </c>
+      <c r="T3" s="3">
+        <f t="shared" ref="T3:T34" si="7">COUNTIF(M3:R3,"SUP")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="L4" s="11"/>
-      <c r="M4" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="S4" s="11"/>
-      <c r="T4" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="U4" s="8" t="s">
-        <v>119</v>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4">
+        <v>153.196</v>
+      </c>
+      <c r="F4">
+        <v>153.036</v>
+      </c>
+      <c r="G4">
+        <v>152.911</v>
+      </c>
+      <c r="H4">
+        <v>153.26900000000001</v>
+      </c>
+      <c r="I4">
+        <v>152.56100000000001</v>
+      </c>
+      <c r="J4">
+        <v>152.60300000000001</v>
+      </c>
+      <c r="K4">
+        <v>152.77000000000001</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>SUP</v>
+      </c>
+      <c r="N4" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>SUP</v>
+      </c>
+      <c r="O4" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>RES</v>
+      </c>
+      <c r="P4" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>SUP</v>
+      </c>
+      <c r="Q4" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>SUP</v>
+      </c>
+      <c r="R4" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>SUP</v>
+      </c>
+      <c r="S4" s="2">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="T4" s="3">
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -4640,67 +4761,66 @@
         <v>103</v>
       </c>
       <c r="E5">
-        <v>153.249</v>
+        <v>153.05000000000001</v>
       </c>
       <c r="F5">
-        <v>153.03800000000001</v>
+        <v>153.03299999999999</v>
       </c>
       <c r="G5">
-        <v>152.911</v>
+        <v>152.91</v>
       </c>
       <c r="H5">
-        <v>153.27099999999999</v>
+        <v>153.268</v>
       </c>
       <c r="I5">
-        <v>152.56</v>
+        <v>152.56200000000001</v>
       </c>
       <c r="J5">
-        <v>152.60300000000001</v>
+        <v>152.602</v>
       </c>
       <c r="K5">
-        <v>152.768</v>
+        <v>152.77099999999999</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1" t="str">
-        <f t="shared" ref="M5:M36" si="0">IF($E5&gt;F5,"SUP","RES")</f>
+        <f t="shared" si="0"/>
         <v>SUP</v>
       </c>
       <c r="N5" s="1" t="str">
-        <f t="shared" ref="N5:N36" si="1">IF($E5&gt;G5,"SUP","RES")</f>
+        <f t="shared" si="1"/>
         <v>SUP</v>
       </c>
       <c r="O5" s="1" t="str">
-        <f t="shared" ref="O5:O36" si="2">IF($E5&gt;H5,"SUP","RES")</f>
+        <f t="shared" si="2"/>
         <v>RES</v>
       </c>
       <c r="P5" s="1" t="str">
-        <f t="shared" ref="P5:P36" si="3">IF($E5&gt;I5,"SUP","RES")</f>
+        <f t="shared" si="3"/>
         <v>SUP</v>
       </c>
       <c r="Q5" s="1" t="str">
-        <f t="shared" ref="Q5:Q36" si="4">IF($E5&gt;J5,"SUP","RES")</f>
+        <f t="shared" si="4"/>
         <v>SUP</v>
       </c>
       <c r="R5" s="1" t="str">
-        <f t="shared" ref="R5:R36" si="5">IF($E5&gt;K5,"SUP","RES")</f>
-        <v>SUP</v>
-      </c>
-      <c r="S5" s="1"/>
-      <c r="T5" s="2">
-        <f t="shared" ref="T5:T36" si="6">COUNTIF(M5:R5,"RES")</f>
+        <f t="shared" si="5"/>
+        <v>SUP</v>
+      </c>
+      <c r="S5" s="2">
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="U5" s="3">
-        <f t="shared" ref="U5:U36" si="7">COUNTIF(M5:R5,"SUP")</f>
+      <c r="T5" s="3">
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -4709,25 +4829,25 @@
         <v>103</v>
       </c>
       <c r="E6">
-        <v>153.196</v>
+        <v>153.06700000000001</v>
       </c>
       <c r="F6">
-        <v>153.036</v>
+        <v>153.03100000000001</v>
       </c>
       <c r="G6">
-        <v>152.911</v>
+        <v>152.91</v>
       </c>
       <c r="H6">
-        <v>153.26900000000001</v>
+        <v>153.26599999999999</v>
       </c>
       <c r="I6">
-        <v>152.56100000000001</v>
+        <v>152.56200000000001</v>
       </c>
       <c r="J6">
-        <v>152.60300000000001</v>
+        <v>152.602</v>
       </c>
       <c r="K6">
-        <v>152.77000000000001</v>
+        <v>152.773</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1" t="str">
@@ -4754,22 +4874,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S6" s="1"/>
-      <c r="T6" s="2">
+      <c r="S6" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="U6" s="3">
+      <c r="T6" s="3">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
@@ -4778,25 +4897,25 @@
         <v>103</v>
       </c>
       <c r="E7">
-        <v>153.05000000000001</v>
+        <v>153.042</v>
       </c>
       <c r="F7">
-        <v>153.03299999999999</v>
+        <v>153.029</v>
       </c>
       <c r="G7">
         <v>152.91</v>
       </c>
       <c r="H7">
-        <v>153.268</v>
+        <v>153.26400000000001</v>
       </c>
       <c r="I7">
-        <v>152.56200000000001</v>
+        <v>152.56299999999999</v>
       </c>
       <c r="J7">
         <v>152.602</v>
       </c>
       <c r="K7">
-        <v>152.77099999999999</v>
+        <v>152.774</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1" t="str">
@@ -4823,22 +4942,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S7" s="1"/>
-      <c r="T7" s="2">
+      <c r="S7" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="U7" s="3">
+      <c r="T7" s="3">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
@@ -4847,25 +4965,25 @@
         <v>103</v>
       </c>
       <c r="E8">
-        <v>153.06700000000001</v>
+        <v>153.05000000000001</v>
       </c>
       <c r="F8">
-        <v>153.03100000000001</v>
+        <v>153.02600000000001</v>
       </c>
       <c r="G8">
-        <v>152.91</v>
+        <v>152.90899999999999</v>
       </c>
       <c r="H8">
-        <v>153.26599999999999</v>
+        <v>153.26300000000001</v>
       </c>
       <c r="I8">
-        <v>152.56200000000001</v>
+        <v>152.56399999999999</v>
       </c>
       <c r="J8">
         <v>152.602</v>
       </c>
       <c r="K8">
-        <v>152.773</v>
+        <v>152.77600000000001</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1" t="str">
@@ -4892,22 +5010,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S8" s="1"/>
-      <c r="T8" s="2">
+      <c r="S8" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="U8" s="3">
+      <c r="T8" s="3">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
@@ -4916,25 +5033,25 @@
         <v>103</v>
       </c>
       <c r="E9">
-        <v>153.042</v>
+        <v>153.03299999999999</v>
       </c>
       <c r="F9">
-        <v>153.029</v>
+        <v>153.024</v>
       </c>
       <c r="G9">
-        <v>152.91</v>
+        <v>152.90899999999999</v>
       </c>
       <c r="H9">
-        <v>153.26400000000001</v>
+        <v>153.261</v>
       </c>
       <c r="I9">
-        <v>152.56299999999999</v>
+        <v>152.565</v>
       </c>
       <c r="J9">
         <v>152.602</v>
       </c>
       <c r="K9">
-        <v>152.774</v>
+        <v>152.77799999999999</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1" t="str">
@@ -4961,22 +5078,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S9" s="1"/>
-      <c r="T9" s="2">
+      <c r="S9" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="U9" s="3">
+      <c r="T9" s="3">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
@@ -4985,30 +5101,30 @@
         <v>103</v>
       </c>
       <c r="E10">
-        <v>153.05000000000001</v>
+        <v>152.999</v>
       </c>
       <c r="F10">
-        <v>153.02600000000001</v>
+        <v>153.02099999999999</v>
       </c>
       <c r="G10">
-        <v>152.90899999999999</v>
+        <v>152.90799999999999</v>
       </c>
       <c r="H10">
-        <v>153.26300000000001</v>
+        <v>153.25899999999999</v>
       </c>
       <c r="I10">
-        <v>152.56399999999999</v>
+        <v>152.565</v>
       </c>
       <c r="J10">
-        <v>152.602</v>
+        <v>152.601</v>
       </c>
       <c r="K10">
-        <v>152.77600000000001</v>
+        <v>152.779</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>SUP</v>
+        <v>RES</v>
       </c>
       <c r="N10" s="1" t="str">
         <f t="shared" si="1"/>
@@ -5030,22 +5146,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S10" s="1"/>
-      <c r="T10" s="2">
+      <c r="S10" s="2">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="U10" s="3">
+        <v>2</v>
+      </c>
+      <c r="T10" s="3">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
@@ -5054,30 +5169,30 @@
         <v>103</v>
       </c>
       <c r="E11">
-        <v>153.03299999999999</v>
+        <v>152.999</v>
       </c>
       <c r="F11">
-        <v>153.024</v>
+        <v>153.01900000000001</v>
       </c>
       <c r="G11">
-        <v>152.90899999999999</v>
+        <v>152.90799999999999</v>
       </c>
       <c r="H11">
-        <v>153.261</v>
+        <v>153.25800000000001</v>
       </c>
       <c r="I11">
-        <v>152.565</v>
+        <v>152.566</v>
       </c>
       <c r="J11">
-        <v>152.602</v>
+        <v>152.601</v>
       </c>
       <c r="K11">
-        <v>152.77799999999999</v>
+        <v>152.78100000000001</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>SUP</v>
+        <v>RES</v>
       </c>
       <c r="N11" s="1" t="str">
         <f t="shared" si="1"/>
@@ -5099,22 +5214,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S11" s="1"/>
-      <c r="T11" s="2">
+      <c r="S11" s="2">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="U11" s="3">
+        <v>2</v>
+      </c>
+      <c r="T11" s="3">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
@@ -5123,25 +5237,25 @@
         <v>103</v>
       </c>
       <c r="E12">
-        <v>152.999</v>
+        <v>152.89699999999999</v>
       </c>
       <c r="F12">
-        <v>153.02099999999999</v>
+        <v>153.01599999999999</v>
       </c>
       <c r="G12">
         <v>152.90799999999999</v>
       </c>
       <c r="H12">
-        <v>153.25899999999999</v>
+        <v>153.256</v>
       </c>
       <c r="I12">
-        <v>152.565</v>
+        <v>152.56700000000001</v>
       </c>
       <c r="J12">
         <v>152.601</v>
       </c>
       <c r="K12">
-        <v>152.779</v>
+        <v>152.78200000000001</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="str">
@@ -5150,7 +5264,7 @@
       </c>
       <c r="N12" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>SUP</v>
+        <v>RES</v>
       </c>
       <c r="O12" s="1" t="str">
         <f t="shared" si="2"/>
@@ -5168,22 +5282,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S12" s="1"/>
-      <c r="T12" s="2">
+      <c r="S12" s="2">
         <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="U12" s="3">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
@@ -5192,25 +5305,25 @@
         <v>103</v>
       </c>
       <c r="E13">
-        <v>152.999</v>
+        <v>152.91</v>
       </c>
       <c r="F13">
-        <v>153.01900000000001</v>
+        <v>153.01400000000001</v>
       </c>
       <c r="G13">
-        <v>152.90799999999999</v>
+        <v>152.90700000000001</v>
       </c>
       <c r="H13">
-        <v>153.25800000000001</v>
+        <v>153.255</v>
       </c>
       <c r="I13">
-        <v>152.566</v>
+        <v>152.56800000000001</v>
       </c>
       <c r="J13">
         <v>152.601</v>
       </c>
       <c r="K13">
-        <v>152.78100000000001</v>
+        <v>152.78399999999999</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1" t="str">
@@ -5237,22 +5350,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S13" s="1"/>
-      <c r="T13" s="2">
+      <c r="S13" s="2">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="U13" s="3">
+      <c r="T13" s="3">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
@@ -5261,25 +5373,25 @@
         <v>103</v>
       </c>
       <c r="E14">
-        <v>152.89699999999999</v>
+        <v>152.87700000000001</v>
       </c>
       <c r="F14">
-        <v>153.01599999999999</v>
+        <v>153.012</v>
       </c>
       <c r="G14">
-        <v>152.90799999999999</v>
+        <v>152.90700000000001</v>
       </c>
       <c r="H14">
-        <v>153.256</v>
+        <v>153.25299999999999</v>
       </c>
       <c r="I14">
-        <v>152.56700000000001</v>
+        <v>152.56899999999999</v>
       </c>
       <c r="J14">
-        <v>152.601</v>
+        <v>152.6</v>
       </c>
       <c r="K14">
-        <v>152.78200000000001</v>
+        <v>152.785</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1" t="str">
@@ -5306,22 +5418,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S14" s="1"/>
-      <c r="T14" s="2">
+      <c r="S14" s="2">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="U14" s="3">
+      <c r="T14" s="3">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
@@ -5330,25 +5441,25 @@
         <v>103</v>
       </c>
       <c r="E15">
-        <v>152.91</v>
+        <v>152.96600000000001</v>
       </c>
       <c r="F15">
-        <v>153.01400000000001</v>
+        <v>153.00899999999999</v>
       </c>
       <c r="G15">
         <v>152.90700000000001</v>
       </c>
       <c r="H15">
-        <v>153.255</v>
+        <v>153.251</v>
       </c>
       <c r="I15">
-        <v>152.56800000000001</v>
+        <v>152.56899999999999</v>
       </c>
       <c r="J15">
-        <v>152.601</v>
+        <v>152.6</v>
       </c>
       <c r="K15">
-        <v>152.78399999999999</v>
+        <v>152.78700000000001</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1" t="str">
@@ -5375,22 +5486,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S15" s="1"/>
-      <c r="T15" s="2">
+      <c r="S15" s="2">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="U15" s="3">
+      <c r="T15" s="3">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
@@ -5399,34 +5509,34 @@
         <v>103</v>
       </c>
       <c r="E16">
-        <v>152.87700000000001</v>
+        <v>153.02000000000001</v>
       </c>
       <c r="F16">
-        <v>153.012</v>
+        <v>153.00700000000001</v>
       </c>
       <c r="G16">
-        <v>152.90700000000001</v>
+        <v>152.90600000000001</v>
       </c>
       <c r="H16">
-        <v>153.25299999999999</v>
+        <v>153.25</v>
       </c>
       <c r="I16">
-        <v>152.56899999999999</v>
+        <v>152.57</v>
       </c>
       <c r="J16">
         <v>152.6</v>
       </c>
       <c r="K16">
-        <v>152.785</v>
+        <v>152.78899999999999</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>RES</v>
+        <v>SUP</v>
       </c>
       <c r="N16" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>RES</v>
+        <v>SUP</v>
       </c>
       <c r="O16" s="1" t="str">
         <f t="shared" si="2"/>
@@ -5444,22 +5554,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S16" s="1"/>
-      <c r="T16" s="2">
+      <c r="S16" s="2">
         <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="U16" s="3">
+        <v>1</v>
+      </c>
+      <c r="T16" s="3">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
         <v>4</v>
@@ -5468,30 +5577,30 @@
         <v>103</v>
       </c>
       <c r="E17">
-        <v>152.96600000000001</v>
+        <v>153.04900000000001</v>
       </c>
       <c r="F17">
-        <v>153.00899999999999</v>
+        <v>153.00399999999999</v>
       </c>
       <c r="G17">
-        <v>152.90700000000001</v>
+        <v>152.90600000000001</v>
       </c>
       <c r="H17">
-        <v>153.251</v>
+        <v>153.24799999999999</v>
       </c>
       <c r="I17">
-        <v>152.56899999999999</v>
+        <v>152.571</v>
       </c>
       <c r="J17">
         <v>152.6</v>
       </c>
       <c r="K17">
-        <v>152.78700000000001</v>
+        <v>152.79</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>RES</v>
+        <v>SUP</v>
       </c>
       <c r="N17" s="1" t="str">
         <f t="shared" si="1"/>
@@ -5513,22 +5622,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S17" s="1"/>
-      <c r="T17" s="2">
+      <c r="S17" s="2">
         <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="U17" s="3">
+        <v>1</v>
+      </c>
+      <c r="T17" s="3">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
         <v>4</v>
@@ -5537,25 +5645,25 @@
         <v>103</v>
       </c>
       <c r="E18">
-        <v>153.02000000000001</v>
+        <v>153.04499999999999</v>
       </c>
       <c r="F18">
-        <v>153.00700000000001</v>
+        <v>153.00200000000001</v>
       </c>
       <c r="G18">
-        <v>152.90600000000001</v>
+        <v>152.905</v>
       </c>
       <c r="H18">
-        <v>153.25</v>
+        <v>153.24600000000001</v>
       </c>
       <c r="I18">
-        <v>152.57</v>
+        <v>152.572</v>
       </c>
       <c r="J18">
-        <v>152.6</v>
+        <v>152.59899999999999</v>
       </c>
       <c r="K18">
-        <v>152.78899999999999</v>
+        <v>152.792</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1" t="str">
@@ -5582,22 +5690,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S18" s="1"/>
-      <c r="T18" s="2">
+      <c r="S18" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="U18" s="3">
+      <c r="T18" s="3">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
         <v>4</v>
@@ -5606,30 +5713,30 @@
         <v>103</v>
       </c>
       <c r="E19">
-        <v>153.04900000000001</v>
+        <v>152.96199999999999</v>
       </c>
       <c r="F19">
-        <v>153.00399999999999</v>
+        <v>152.999</v>
       </c>
       <c r="G19">
-        <v>152.90600000000001</v>
+        <v>152.905</v>
       </c>
       <c r="H19">
-        <v>153.24799999999999</v>
+        <v>153.245</v>
       </c>
       <c r="I19">
-        <v>152.571</v>
+        <v>152.572</v>
       </c>
       <c r="J19">
-        <v>152.6</v>
+        <v>152.59899999999999</v>
       </c>
       <c r="K19">
-        <v>152.79</v>
+        <v>152.79300000000001</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>SUP</v>
+        <v>RES</v>
       </c>
       <c r="N19" s="1" t="str">
         <f t="shared" si="1"/>
@@ -5651,22 +5758,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S19" s="1"/>
-      <c r="T19" s="2">
+      <c r="S19" s="2">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="U19" s="3">
+        <v>2</v>
+      </c>
+      <c r="T19" s="3">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
         <v>4</v>
@@ -5675,25 +5781,25 @@
         <v>103</v>
       </c>
       <c r="E20">
-        <v>153.04499999999999</v>
+        <v>153.04599999999999</v>
       </c>
       <c r="F20">
-        <v>153.00200000000001</v>
+        <v>152.99700000000001</v>
       </c>
       <c r="G20">
         <v>152.905</v>
       </c>
       <c r="H20">
-        <v>153.24600000000001</v>
+        <v>153.24299999999999</v>
       </c>
       <c r="I20">
-        <v>152.572</v>
+        <v>152.57300000000001</v>
       </c>
       <c r="J20">
         <v>152.59899999999999</v>
       </c>
       <c r="K20">
-        <v>152.792</v>
+        <v>152.79499999999999</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1" t="str">
@@ -5720,22 +5826,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S20" s="1"/>
-      <c r="T20" s="2">
+      <c r="S20" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="U20" s="3">
+      <c r="T20" s="3">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
         <v>4</v>
@@ -5744,30 +5849,30 @@
         <v>103</v>
       </c>
       <c r="E21">
-        <v>152.96199999999999</v>
+        <v>153.04599999999999</v>
       </c>
       <c r="F21">
-        <v>152.999</v>
+        <v>152.995</v>
       </c>
       <c r="G21">
-        <v>152.905</v>
+        <v>152.904</v>
       </c>
       <c r="H21">
-        <v>153.245</v>
+        <v>153.24100000000001</v>
       </c>
       <c r="I21">
-        <v>152.572</v>
+        <v>152.57400000000001</v>
       </c>
       <c r="J21">
         <v>152.59899999999999</v>
       </c>
       <c r="K21">
-        <v>152.79300000000001</v>
+        <v>152.79599999999999</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>RES</v>
+        <v>SUP</v>
       </c>
       <c r="N21" s="1" t="str">
         <f t="shared" si="1"/>
@@ -5789,22 +5894,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S21" s="1"/>
-      <c r="T21" s="2">
+      <c r="S21" s="2">
         <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="U21" s="3">
+        <v>1</v>
+      </c>
+      <c r="T21" s="3">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
         <v>4</v>
@@ -5813,25 +5917,25 @@
         <v>103</v>
       </c>
       <c r="E22">
-        <v>153.04599999999999</v>
+        <v>153.09</v>
       </c>
       <c r="F22">
-        <v>152.99700000000001</v>
+        <v>152.99199999999999</v>
       </c>
       <c r="G22">
-        <v>152.905</v>
+        <v>152.904</v>
       </c>
       <c r="H22">
-        <v>153.24299999999999</v>
+        <v>153.24</v>
       </c>
       <c r="I22">
-        <v>152.57300000000001</v>
+        <v>152.57499999999999</v>
       </c>
       <c r="J22">
         <v>152.59899999999999</v>
       </c>
       <c r="K22">
-        <v>152.79499999999999</v>
+        <v>152.798</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1" t="str">
@@ -5858,22 +5962,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S22" s="1"/>
-      <c r="T22" s="2">
+      <c r="S22" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="U22" s="3">
+      <c r="T22" s="3">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
@@ -5882,25 +5985,25 @@
         <v>103</v>
       </c>
       <c r="E23">
-        <v>153.04599999999999</v>
+        <v>153.001</v>
       </c>
       <c r="F23">
-        <v>152.995</v>
+        <v>152.99</v>
       </c>
       <c r="G23">
         <v>152.904</v>
       </c>
       <c r="H23">
-        <v>153.24100000000001</v>
+        <v>153.238</v>
       </c>
       <c r="I23">
-        <v>152.57400000000001</v>
+        <v>152.57499999999999</v>
       </c>
       <c r="J23">
-        <v>152.59899999999999</v>
+        <v>152.59800000000001</v>
       </c>
       <c r="K23">
-        <v>152.79599999999999</v>
+        <v>152.80000000000001</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="str">
@@ -5927,22 +6030,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S23" s="1"/>
-      <c r="T23" s="2">
+      <c r="S23" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="U23" s="3">
+      <c r="T23" s="3">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
         <v>4</v>
@@ -5951,25 +6053,25 @@
         <v>103</v>
       </c>
       <c r="E24">
-        <v>153.09</v>
+        <v>153.036</v>
       </c>
       <c r="F24">
-        <v>152.99199999999999</v>
+        <v>152.98699999999999</v>
       </c>
       <c r="G24">
-        <v>152.904</v>
+        <v>152.90299999999999</v>
       </c>
       <c r="H24">
-        <v>153.24</v>
+        <v>153.23599999999999</v>
       </c>
       <c r="I24">
-        <v>152.57499999999999</v>
+        <v>152.57599999999999</v>
       </c>
       <c r="J24">
-        <v>152.59899999999999</v>
+        <v>152.59800000000001</v>
       </c>
       <c r="K24">
-        <v>152.798</v>
+        <v>152.80099999999999</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="str">
@@ -5996,22 +6098,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S24" s="1"/>
-      <c r="T24" s="2">
+      <c r="S24" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="U24" s="3">
+      <c r="T24" s="3">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
         <v>4</v>
@@ -6020,25 +6121,25 @@
         <v>103</v>
       </c>
       <c r="E25">
-        <v>153.001</v>
+        <v>153.07499999999999</v>
       </c>
       <c r="F25">
-        <v>152.99</v>
+        <v>152.98500000000001</v>
       </c>
       <c r="G25">
-        <v>152.904</v>
+        <v>152.90299999999999</v>
       </c>
       <c r="H25">
-        <v>153.238</v>
+        <v>153.23500000000001</v>
       </c>
       <c r="I25">
-        <v>152.57499999999999</v>
+        <v>152.577</v>
       </c>
       <c r="J25">
         <v>152.59800000000001</v>
       </c>
       <c r="K25">
-        <v>152.80000000000001</v>
+        <v>152.803</v>
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1" t="str">
@@ -6065,22 +6166,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S25" s="1"/>
-      <c r="T25" s="2">
+      <c r="S25" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="U25" s="3">
+      <c r="T25" s="3">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
         <v>4</v>
@@ -6089,25 +6189,25 @@
         <v>103</v>
       </c>
       <c r="E26">
-        <v>153.036</v>
+        <v>153.072</v>
       </c>
       <c r="F26">
-        <v>152.98699999999999</v>
+        <v>152.983</v>
       </c>
       <c r="G26">
         <v>152.90299999999999</v>
       </c>
       <c r="H26">
-        <v>153.23599999999999</v>
+        <v>153.233</v>
       </c>
       <c r="I26">
-        <v>152.57599999999999</v>
+        <v>152.578</v>
       </c>
       <c r="J26">
         <v>152.59800000000001</v>
       </c>
       <c r="K26">
-        <v>152.80099999999999</v>
+        <v>152.804</v>
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1" t="str">
@@ -6134,22 +6234,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S26" s="1"/>
-      <c r="T26" s="2">
+      <c r="S26" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="U26" s="3">
+      <c r="T26" s="3">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
         <v>4</v>
@@ -6158,30 +6257,30 @@
         <v>103</v>
       </c>
       <c r="E27">
-        <v>153.07499999999999</v>
+        <v>152.95099999999999</v>
       </c>
       <c r="F27">
-        <v>152.98500000000001</v>
+        <v>152.97999999999999</v>
       </c>
       <c r="G27">
-        <v>152.90299999999999</v>
+        <v>152.90199999999999</v>
       </c>
       <c r="H27">
-        <v>153.23500000000001</v>
+        <v>153.232</v>
       </c>
       <c r="I27">
-        <v>152.577</v>
+        <v>152.578</v>
       </c>
       <c r="J27">
-        <v>152.59800000000001</v>
+        <v>152.59700000000001</v>
       </c>
       <c r="K27">
-        <v>152.803</v>
+        <v>152.80600000000001</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>SUP</v>
+        <v>RES</v>
       </c>
       <c r="N27" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6203,22 +6302,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S27" s="1"/>
-      <c r="T27" s="2">
+      <c r="S27" s="2">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="U27" s="3">
+        <v>2</v>
+      </c>
+      <c r="T27" s="3">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
@@ -6227,30 +6325,30 @@
         <v>103</v>
       </c>
       <c r="E28">
-        <v>153.072</v>
+        <v>152.94800000000001</v>
       </c>
       <c r="F28">
-        <v>152.983</v>
+        <v>152.97800000000001</v>
       </c>
       <c r="G28">
-        <v>152.90299999999999</v>
+        <v>152.90199999999999</v>
       </c>
       <c r="H28">
-        <v>153.233</v>
+        <v>153.22999999999999</v>
       </c>
       <c r="I28">
-        <v>152.578</v>
+        <v>152.57900000000001</v>
       </c>
       <c r="J28">
-        <v>152.59800000000001</v>
+        <v>152.59700000000001</v>
       </c>
       <c r="K28">
-        <v>152.804</v>
+        <v>152.80799999999999</v>
       </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>SUP</v>
+        <v>RES</v>
       </c>
       <c r="N28" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6272,22 +6370,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S28" s="1"/>
-      <c r="T28" s="2">
+      <c r="S28" s="2">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="U28" s="3">
+        <v>2</v>
+      </c>
+      <c r="T28" s="3">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
         <v>4</v>
@@ -6296,30 +6393,30 @@
         <v>103</v>
       </c>
       <c r="E29">
-        <v>152.95099999999999</v>
+        <v>153.006</v>
       </c>
       <c r="F29">
-        <v>152.97999999999999</v>
+        <v>152.97499999999999</v>
       </c>
       <c r="G29">
-        <v>152.90199999999999</v>
+        <v>152.90100000000001</v>
       </c>
       <c r="H29">
-        <v>153.232</v>
+        <v>153.22800000000001</v>
       </c>
       <c r="I29">
-        <v>152.578</v>
+        <v>152.58000000000001</v>
       </c>
       <c r="J29">
         <v>152.59700000000001</v>
       </c>
       <c r="K29">
-        <v>152.80600000000001</v>
+        <v>152.809</v>
       </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>RES</v>
+        <v>SUP</v>
       </c>
       <c r="N29" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6341,22 +6438,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S29" s="1"/>
-      <c r="T29" s="2">
+      <c r="S29" s="2">
         <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="U29" s="3">
+        <v>1</v>
+      </c>
+      <c r="T29" s="3">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -6365,30 +6461,30 @@
         <v>103</v>
       </c>
       <c r="E30">
-        <v>152.94800000000001</v>
+        <v>153.13200000000001</v>
       </c>
       <c r="F30">
-        <v>152.97800000000001</v>
+        <v>152.97300000000001</v>
       </c>
       <c r="G30">
-        <v>152.90199999999999</v>
+        <v>152.90100000000001</v>
       </c>
       <c r="H30">
-        <v>153.22999999999999</v>
+        <v>153.227</v>
       </c>
       <c r="I30">
-        <v>152.57900000000001</v>
+        <v>152.58099999999999</v>
       </c>
       <c r="J30">
         <v>152.59700000000001</v>
       </c>
       <c r="K30">
-        <v>152.80799999999999</v>
+        <v>152.81100000000001</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>RES</v>
+        <v>SUP</v>
       </c>
       <c r="N30" s="1" t="str">
         <f t="shared" si="1"/>
@@ -6410,22 +6506,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S30" s="1"/>
-      <c r="T30" s="2">
+      <c r="S30" s="2">
         <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="U30" s="3">
+        <v>1</v>
+      </c>
+      <c r="T30" s="3">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C31" t="s">
         <v>4</v>
@@ -6434,25 +6529,25 @@
         <v>103</v>
       </c>
       <c r="E31">
-        <v>153.006</v>
+        <v>153.16499999999999</v>
       </c>
       <c r="F31">
-        <v>152.97499999999999</v>
+        <v>152.97</v>
       </c>
       <c r="G31">
         <v>152.90100000000001</v>
       </c>
       <c r="H31">
-        <v>153.22800000000001</v>
+        <v>153.22499999999999</v>
       </c>
       <c r="I31">
-        <v>152.58000000000001</v>
+        <v>152.58199999999999</v>
       </c>
       <c r="J31">
-        <v>152.59700000000001</v>
+        <v>152.596</v>
       </c>
       <c r="K31">
-        <v>152.809</v>
+        <v>152.81200000000001</v>
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1" t="str">
@@ -6479,22 +6574,21 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S31" s="1"/>
-      <c r="T31" s="2">
+      <c r="S31" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="U31" s="3">
+      <c r="T31" s="3">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C32" t="s">
         <v>4</v>
@@ -6503,25 +6597,25 @@
         <v>103</v>
       </c>
       <c r="E32">
-        <v>153.13200000000001</v>
+        <v>153.161</v>
       </c>
       <c r="F32">
-        <v>152.97300000000001</v>
+        <v>152.96799999999999</v>
       </c>
       <c r="G32">
-        <v>152.90100000000001</v>
+        <v>152.9</v>
       </c>
       <c r="H32">
-        <v>153.227</v>
+        <v>153.22300000000001</v>
       </c>
       <c r="I32">
-        <v>152.58099999999999</v>
+        <v>152.58199999999999</v>
       </c>
       <c r="J32">
-        <v>152.59700000000001</v>
+        <v>152.596</v>
       </c>
       <c r="K32">
-        <v>152.81100000000001</v>
+        <v>152.81399999999999</v>
       </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1" t="str">
@@ -6548,298 +6642,293 @@
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S32" s="1"/>
-      <c r="T32" s="2">
+      <c r="S32" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="U32" s="3">
+      <c r="T32" s="3">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33">
-        <v>29</v>
-      </c>
-      <c r="B33" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D33" t="s">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="4">
+        <v>31</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E33">
-        <v>153.16499999999999</v>
-      </c>
-      <c r="F33">
-        <v>152.97</v>
-      </c>
-      <c r="G33">
-        <v>152.90100000000001</v>
-      </c>
-      <c r="H33">
-        <v>153.22499999999999</v>
-      </c>
-      <c r="I33">
-        <v>152.58199999999999</v>
-      </c>
-      <c r="J33">
+      <c r="E33" s="4">
+        <v>153.053</v>
+      </c>
+      <c r="F33" s="4">
+        <v>152.96600000000001</v>
+      </c>
+      <c r="G33" s="4">
+        <v>152.9</v>
+      </c>
+      <c r="H33" s="4">
+        <v>153.22200000000001</v>
+      </c>
+      <c r="I33" s="4">
+        <v>152.583</v>
+      </c>
+      <c r="J33" s="4">
         <v>152.596</v>
       </c>
-      <c r="K33">
-        <v>152.81200000000001</v>
-      </c>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1" t="str">
+      <c r="K33" s="4">
+        <v>152.815</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5" t="str">
         <f t="shared" si="0"/>
         <v>SUP</v>
       </c>
-      <c r="N33" s="1" t="str">
+      <c r="N33" s="5" t="str">
         <f t="shared" si="1"/>
         <v>SUP</v>
       </c>
-      <c r="O33" s="1" t="str">
+      <c r="O33" s="5" t="str">
         <f t="shared" si="2"/>
         <v>RES</v>
       </c>
-      <c r="P33" s="1" t="str">
+      <c r="P33" s="5" t="str">
         <f t="shared" si="3"/>
         <v>SUP</v>
       </c>
-      <c r="Q33" s="1" t="str">
+      <c r="Q33" s="5" t="str">
         <f t="shared" si="4"/>
         <v>SUP</v>
       </c>
-      <c r="R33" s="1" t="str">
+      <c r="R33" s="5" t="str">
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S33" s="1"/>
-      <c r="T33" s="2">
+      <c r="S33" s="6">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="U33" s="3">
+      <c r="T33" s="7">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34">
-        <v>30</v>
-      </c>
-      <c r="B34" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" t="s">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="4">
+        <v>32</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E34">
-        <v>153.161</v>
-      </c>
-      <c r="F34">
-        <v>152.96799999999999</v>
-      </c>
-      <c r="G34">
+      <c r="E34" s="4">
+        <v>153.05699999999999</v>
+      </c>
+      <c r="F34" s="4">
+        <v>152.96299999999999</v>
+      </c>
+      <c r="G34" s="4">
         <v>152.9</v>
       </c>
-      <c r="H34">
-        <v>153.22300000000001</v>
-      </c>
-      <c r="I34">
-        <v>152.58199999999999</v>
-      </c>
-      <c r="J34">
+      <c r="H34" s="4">
+        <v>153.22</v>
+      </c>
+      <c r="I34" s="4">
+        <v>152.584</v>
+      </c>
+      <c r="J34" s="4">
         <v>152.596</v>
       </c>
-      <c r="K34">
-        <v>152.81399999999999</v>
-      </c>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1" t="str">
+      <c r="K34" s="4">
+        <v>152.81700000000001</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5" t="str">
         <f t="shared" si="0"/>
         <v>SUP</v>
       </c>
-      <c r="N34" s="1" t="str">
+      <c r="N34" s="5" t="str">
         <f t="shared" si="1"/>
         <v>SUP</v>
       </c>
-      <c r="O34" s="1" t="str">
+      <c r="O34" s="5" t="str">
         <f t="shared" si="2"/>
         <v>RES</v>
       </c>
-      <c r="P34" s="1" t="str">
+      <c r="P34" s="5" t="str">
         <f t="shared" si="3"/>
         <v>SUP</v>
       </c>
-      <c r="Q34" s="1" t="str">
+      <c r="Q34" s="5" t="str">
         <f t="shared" si="4"/>
         <v>SUP</v>
       </c>
-      <c r="R34" s="1" t="str">
+      <c r="R34" s="5" t="str">
         <f t="shared" si="5"/>
         <v>SUP</v>
       </c>
-      <c r="S34" s="1"/>
-      <c r="T34" s="2">
+      <c r="S34" s="6">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="U34" s="3">
+      <c r="T34" s="7">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="4">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="s">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" t="s">
+        <v>103</v>
+      </c>
+      <c r="E35">
+        <v>152.89500000000001</v>
+      </c>
+      <c r="F35">
+        <v>152.96100000000001</v>
+      </c>
+      <c r="G35">
+        <v>152.899</v>
+      </c>
+      <c r="H35">
+        <v>153.21799999999999</v>
+      </c>
+      <c r="I35">
+        <v>152.58500000000001</v>
+      </c>
+      <c r="J35">
+        <v>152.596</v>
+      </c>
+      <c r="K35">
+        <v>152.81899999999999</v>
+      </c>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1" t="str">
+        <f t="shared" ref="M35:M66" si="8">IF($E35&gt;F35,"SUP","RES")</f>
+        <v>RES</v>
+      </c>
+      <c r="N35" s="1" t="str">
+        <f t="shared" ref="N35:N66" si="9">IF($E35&gt;G35,"SUP","RES")</f>
+        <v>RES</v>
+      </c>
+      <c r="O35" s="1" t="str">
+        <f t="shared" ref="O35:O66" si="10">IF($E35&gt;H35,"SUP","RES")</f>
+        <v>RES</v>
+      </c>
+      <c r="P35" s="1" t="str">
+        <f t="shared" ref="P35:P66" si="11">IF($E35&gt;I35,"SUP","RES")</f>
+        <v>SUP</v>
+      </c>
+      <c r="Q35" s="1" t="str">
+        <f t="shared" ref="Q35:Q66" si="12">IF($E35&gt;J35,"SUP","RES")</f>
+        <v>SUP</v>
+      </c>
+      <c r="R35" s="1" t="str">
+        <f t="shared" ref="R35:R66" si="13">IF($E35&gt;K35,"SUP","RES")</f>
+        <v>SUP</v>
+      </c>
+      <c r="S35" s="2">
+        <f t="shared" ref="S35:S66" si="14">COUNTIF(M35:R35,"RES")</f>
+        <v>3</v>
+      </c>
+      <c r="T35" s="3">
+        <f t="shared" ref="T35:T66" si="15">COUNTIF(M35:R35,"SUP")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36">
         <v>34</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="B36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" t="s">
         <v>103</v>
       </c>
-      <c r="E35" s="4">
-        <v>153.053</v>
-      </c>
-      <c r="F35" s="4">
-        <v>152.96600000000001</v>
-      </c>
-      <c r="G35" s="4">
-        <v>152.9</v>
-      </c>
-      <c r="H35" s="4">
-        <v>153.22200000000001</v>
-      </c>
-      <c r="I35" s="4">
-        <v>152.583</v>
-      </c>
-      <c r="J35" s="4">
-        <v>152.596</v>
-      </c>
-      <c r="K35" s="4">
-        <v>152.815</v>
-      </c>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>SUP</v>
-      </c>
-      <c r="N35" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>SUP</v>
-      </c>
-      <c r="O35" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>RES</v>
-      </c>
-      <c r="P35" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>SUP</v>
-      </c>
-      <c r="Q35" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>SUP</v>
-      </c>
-      <c r="R35" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>SUP</v>
-      </c>
-      <c r="S35" s="5"/>
-      <c r="T35" s="6">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="U35" s="7">
-        <f t="shared" si="7"/>
-        <v>5</v>
+      <c r="E36">
+        <v>152.87</v>
+      </c>
+      <c r="F36">
+        <v>152.958</v>
+      </c>
+      <c r="G36">
+        <v>152.899</v>
+      </c>
+      <c r="H36">
+        <v>153.21700000000001</v>
+      </c>
+      <c r="I36">
+        <v>152.58500000000001</v>
+      </c>
+      <c r="J36">
+        <v>152.595</v>
+      </c>
+      <c r="K36">
+        <v>152.82</v>
+      </c>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>RES</v>
+      </c>
+      <c r="N36" s="1" t="str">
+        <f t="shared" si="9"/>
+        <v>RES</v>
+      </c>
+      <c r="O36" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>RES</v>
+      </c>
+      <c r="P36" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>SUP</v>
+      </c>
+      <c r="Q36" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>SUP</v>
+      </c>
+      <c r="R36" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>SUP</v>
+      </c>
+      <c r="S36" s="2">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="T36" s="3">
+        <f t="shared" si="15"/>
+        <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="4">
-        <v>32</v>
-      </c>
-      <c r="B36" s="4" t="s">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37">
         <v>35</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E36" s="4">
-        <v>153.05699999999999</v>
-      </c>
-      <c r="F36" s="4">
-        <v>152.96299999999999</v>
-      </c>
-      <c r="G36" s="4">
-        <v>152.9</v>
-      </c>
-      <c r="H36" s="4">
-        <v>153.22</v>
-      </c>
-      <c r="I36" s="4">
-        <v>152.584</v>
-      </c>
-      <c r="J36" s="4">
-        <v>152.596</v>
-      </c>
-      <c r="K36" s="4">
-        <v>152.81700000000001</v>
-      </c>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>SUP</v>
-      </c>
-      <c r="N36" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>SUP</v>
-      </c>
-      <c r="O36" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>RES</v>
-      </c>
-      <c r="P36" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>SUP</v>
-      </c>
-      <c r="Q36" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>SUP</v>
-      </c>
-      <c r="R36" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>SUP</v>
-      </c>
-      <c r="S36" s="5"/>
-      <c r="T36" s="6">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="U36" s="7">
-        <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37">
-        <v>33</v>
-      </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C37" t="s">
         <v>4</v>
@@ -6848,67 +6937,66 @@
         <v>103</v>
       </c>
       <c r="E37">
-        <v>152.89500000000001</v>
+        <v>152.86199999999999</v>
       </c>
       <c r="F37">
-        <v>152.96100000000001</v>
+        <v>152.95599999999999</v>
       </c>
       <c r="G37">
-        <v>152.899</v>
+        <v>152.898</v>
       </c>
       <c r="H37">
-        <v>153.21799999999999</v>
+        <v>153.215</v>
       </c>
       <c r="I37">
-        <v>152.58500000000001</v>
+        <v>152.58600000000001</v>
       </c>
       <c r="J37">
-        <v>152.596</v>
+        <v>152.595</v>
       </c>
       <c r="K37">
-        <v>152.81899999999999</v>
+        <v>152.822</v>
       </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1" t="str">
-        <f t="shared" ref="M37:M68" si="8">IF($E37&gt;F37,"SUP","RES")</f>
+        <f t="shared" si="8"/>
         <v>RES</v>
       </c>
       <c r="N37" s="1" t="str">
-        <f t="shared" ref="N37:N68" si="9">IF($E37&gt;G37,"SUP","RES")</f>
+        <f t="shared" si="9"/>
         <v>RES</v>
       </c>
       <c r="O37" s="1" t="str">
-        <f t="shared" ref="O37:O68" si="10">IF($E37&gt;H37,"SUP","RES")</f>
+        <f t="shared" si="10"/>
         <v>RES</v>
       </c>
       <c r="P37" s="1" t="str">
-        <f t="shared" ref="P37:P68" si="11">IF($E37&gt;I37,"SUP","RES")</f>
+        <f t="shared" si="11"/>
         <v>SUP</v>
       </c>
       <c r="Q37" s="1" t="str">
-        <f t="shared" ref="Q37:Q68" si="12">IF($E37&gt;J37,"SUP","RES")</f>
+        <f t="shared" si="12"/>
         <v>SUP</v>
       </c>
       <c r="R37" s="1" t="str">
-        <f t="shared" ref="R37:R68" si="13">IF($E37&gt;K37,"SUP","RES")</f>
-        <v>SUP</v>
-      </c>
-      <c r="S37" s="1"/>
-      <c r="T37" s="2">
-        <f t="shared" ref="T37:T68" si="14">COUNTIF(M37:R37,"RES")</f>
+        <f t="shared" si="13"/>
+        <v>SUP</v>
+      </c>
+      <c r="S37" s="2">
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-      <c r="U37" s="3">
-        <f t="shared" ref="U37:U68" si="15">COUNTIF(M37:R37,"SUP")</f>
+      <c r="T37" s="3">
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C38" t="s">
         <v>4</v>
@@ -6917,25 +7005,25 @@
         <v>103</v>
       </c>
       <c r="E38">
-        <v>152.87</v>
+        <v>152.89400000000001</v>
       </c>
       <c r="F38">
-        <v>152.958</v>
+        <v>152.953</v>
       </c>
       <c r="G38">
-        <v>152.899</v>
+        <v>152.898</v>
       </c>
       <c r="H38">
-        <v>153.21700000000001</v>
+        <v>153.214</v>
       </c>
       <c r="I38">
-        <v>152.58500000000001</v>
+        <v>152.58699999999999</v>
       </c>
       <c r="J38">
         <v>152.595</v>
       </c>
       <c r="K38">
-        <v>152.82</v>
+        <v>152.82300000000001</v>
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1" t="str">
@@ -6962,22 +7050,21 @@
         <f t="shared" si="13"/>
         <v>SUP</v>
       </c>
-      <c r="S38" s="1"/>
-      <c r="T38" s="2">
+      <c r="S38" s="2">
         <f t="shared" si="14"/>
         <v>3</v>
       </c>
-      <c r="U38" s="3">
+      <c r="T38" s="3">
         <f t="shared" si="15"/>
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s">
         <v>4</v>
@@ -6986,25 +7073,25 @@
         <v>103</v>
       </c>
       <c r="E39">
-        <v>152.86199999999999</v>
+        <v>152.80699999999999</v>
       </c>
       <c r="F39">
-        <v>152.95599999999999</v>
+        <v>152.95099999999999</v>
       </c>
       <c r="G39">
         <v>152.898</v>
       </c>
       <c r="H39">
-        <v>153.215</v>
+        <v>153.21199999999999</v>
       </c>
       <c r="I39">
-        <v>152.58600000000001</v>
+        <v>152.58799999999999</v>
       </c>
       <c r="J39">
         <v>152.595</v>
       </c>
       <c r="K39">
-        <v>152.822</v>
+        <v>152.82499999999999</v>
       </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1" t="str">
@@ -7029,24 +7116,23 @@
       </c>
       <c r="R39" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>SUP</v>
-      </c>
-      <c r="S39" s="1"/>
-      <c r="T39" s="2">
+        <v>RES</v>
+      </c>
+      <c r="S39" s="2">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="U39" s="3">
+        <v>4</v>
+      </c>
+      <c r="T39" s="3">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C40" t="s">
         <v>4</v>
@@ -7055,25 +7141,25 @@
         <v>103</v>
       </c>
       <c r="E40">
-        <v>152.89400000000001</v>
+        <v>152.81700000000001</v>
       </c>
       <c r="F40">
-        <v>152.953</v>
+        <v>152.94900000000001</v>
       </c>
       <c r="G40">
-        <v>152.898</v>
+        <v>152.89699999999999</v>
       </c>
       <c r="H40">
-        <v>153.214</v>
+        <v>153.21</v>
       </c>
       <c r="I40">
-        <v>152.58699999999999</v>
+        <v>152.58799999999999</v>
       </c>
       <c r="J40">
-        <v>152.595</v>
+        <v>152.59399999999999</v>
       </c>
       <c r="K40">
-        <v>152.82300000000001</v>
+        <v>152.827</v>
       </c>
       <c r="L40" s="1"/>
       <c r="M40" s="1" t="str">
@@ -7098,24 +7184,23 @@
       </c>
       <c r="R40" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>SUP</v>
-      </c>
-      <c r="S40" s="1"/>
-      <c r="T40" s="2">
+        <v>RES</v>
+      </c>
+      <c r="S40" s="2">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="U40" s="3">
+        <v>4</v>
+      </c>
+      <c r="T40" s="3">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C41" t="s">
         <v>4</v>
@@ -7124,25 +7209,25 @@
         <v>103</v>
       </c>
       <c r="E41">
-        <v>152.80699999999999</v>
+        <v>152.77000000000001</v>
       </c>
       <c r="F41">
-        <v>152.95099999999999</v>
+        <v>152.946</v>
       </c>
       <c r="G41">
-        <v>152.898</v>
+        <v>152.89699999999999</v>
       </c>
       <c r="H41">
-        <v>153.21199999999999</v>
+        <v>153.209</v>
       </c>
       <c r="I41">
-        <v>152.58799999999999</v>
+        <v>152.589</v>
       </c>
       <c r="J41">
-        <v>152.595</v>
+        <v>152.59399999999999</v>
       </c>
       <c r="K41">
-        <v>152.82499999999999</v>
+        <v>152.828</v>
       </c>
       <c r="L41" s="1"/>
       <c r="M41" s="1" t="str">
@@ -7169,22 +7254,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S41" s="1"/>
-      <c r="T41" s="2">
+      <c r="S41" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U41" s="3">
+      <c r="T41" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C42" t="s">
         <v>4</v>
@@ -7193,25 +7277,25 @@
         <v>103</v>
       </c>
       <c r="E42">
-        <v>152.81700000000001</v>
+        <v>152.79</v>
       </c>
       <c r="F42">
-        <v>152.94900000000001</v>
+        <v>152.94399999999999</v>
       </c>
       <c r="G42">
         <v>152.89699999999999</v>
       </c>
       <c r="H42">
-        <v>153.21</v>
+        <v>153.20699999999999</v>
       </c>
       <c r="I42">
-        <v>152.58799999999999</v>
+        <v>152.59</v>
       </c>
       <c r="J42">
         <v>152.59399999999999</v>
       </c>
       <c r="K42">
-        <v>152.827</v>
+        <v>152.83000000000001</v>
       </c>
       <c r="L42" s="1"/>
       <c r="M42" s="1" t="str">
@@ -7238,22 +7322,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S42" s="1"/>
-      <c r="T42" s="2">
+      <c r="S42" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U42" s="3">
+      <c r="T42" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C43" t="s">
         <v>4</v>
@@ -7262,25 +7345,25 @@
         <v>103</v>
       </c>
       <c r="E43">
-        <v>152.77000000000001</v>
+        <v>152.78899999999999</v>
       </c>
       <c r="F43">
-        <v>152.946</v>
+        <v>152.941</v>
       </c>
       <c r="G43">
-        <v>152.89699999999999</v>
+        <v>152.89599999999999</v>
       </c>
       <c r="H43">
-        <v>153.209</v>
+        <v>153.20500000000001</v>
       </c>
       <c r="I43">
-        <v>152.589</v>
+        <v>152.59100000000001</v>
       </c>
       <c r="J43">
         <v>152.59399999999999</v>
       </c>
       <c r="K43">
-        <v>152.828</v>
+        <v>152.83099999999999</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1" t="str">
@@ -7307,22 +7390,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S43" s="1"/>
-      <c r="T43" s="2">
+      <c r="S43" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U43" s="3">
+      <c r="T43" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C44" t="s">
         <v>4</v>
@@ -7331,25 +7413,25 @@
         <v>103</v>
       </c>
       <c r="E44">
-        <v>152.79</v>
+        <v>152.75</v>
       </c>
       <c r="F44">
-        <v>152.94399999999999</v>
+        <v>152.93899999999999</v>
       </c>
       <c r="G44">
-        <v>152.89699999999999</v>
+        <v>152.89599999999999</v>
       </c>
       <c r="H44">
-        <v>153.20699999999999</v>
+        <v>153.20400000000001</v>
       </c>
       <c r="I44">
-        <v>152.59</v>
+        <v>152.59100000000001</v>
       </c>
       <c r="J44">
-        <v>152.59399999999999</v>
+        <v>152.59299999999999</v>
       </c>
       <c r="K44">
-        <v>152.83000000000001</v>
+        <v>152.833</v>
       </c>
       <c r="L44" s="1"/>
       <c r="M44" s="1" t="str">
@@ -7376,22 +7458,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S44" s="1"/>
-      <c r="T44" s="2">
+      <c r="S44" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U44" s="3">
+      <c r="T44" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C45" t="s">
         <v>4</v>
@@ -7400,25 +7481,25 @@
         <v>103</v>
       </c>
       <c r="E45">
-        <v>152.78899999999999</v>
+        <v>152.661</v>
       </c>
       <c r="F45">
-        <v>152.941</v>
+        <v>152.93600000000001</v>
       </c>
       <c r="G45">
-        <v>152.89599999999999</v>
+        <v>152.89500000000001</v>
       </c>
       <c r="H45">
-        <v>153.20500000000001</v>
+        <v>153.202</v>
       </c>
       <c r="I45">
-        <v>152.59100000000001</v>
+        <v>152.59200000000001</v>
       </c>
       <c r="J45">
-        <v>152.59399999999999</v>
+        <v>152.59299999999999</v>
       </c>
       <c r="K45">
-        <v>152.83099999999999</v>
+        <v>152.834</v>
       </c>
       <c r="L45" s="1"/>
       <c r="M45" s="1" t="str">
@@ -7445,22 +7526,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S45" s="1"/>
-      <c r="T45" s="2">
+      <c r="S45" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U45" s="3">
+      <c r="T45" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C46" t="s">
         <v>4</v>
@@ -7469,25 +7549,25 @@
         <v>103</v>
       </c>
       <c r="E46">
-        <v>152.75</v>
+        <v>152.672</v>
       </c>
       <c r="F46">
-        <v>152.93899999999999</v>
+        <v>152.934</v>
       </c>
       <c r="G46">
-        <v>152.89599999999999</v>
+        <v>152.89500000000001</v>
       </c>
       <c r="H46">
-        <v>153.20400000000001</v>
+        <v>153.19999999999999</v>
       </c>
       <c r="I46">
-        <v>152.59100000000001</v>
+        <v>152.59299999999999</v>
       </c>
       <c r="J46">
         <v>152.59299999999999</v>
       </c>
       <c r="K46">
-        <v>152.833</v>
+        <v>152.83600000000001</v>
       </c>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="str">
@@ -7514,22 +7594,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S46" s="1"/>
-      <c r="T46" s="2">
+      <c r="S46" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U46" s="3">
+      <c r="T46" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C47" t="s">
         <v>4</v>
@@ -7538,25 +7617,25 @@
         <v>103</v>
       </c>
       <c r="E47">
-        <v>152.661</v>
+        <v>152.738</v>
       </c>
       <c r="F47">
-        <v>152.93600000000001</v>
+        <v>152.93199999999999</v>
       </c>
       <c r="G47">
         <v>152.89500000000001</v>
       </c>
       <c r="H47">
-        <v>153.202</v>
+        <v>153.19900000000001</v>
       </c>
       <c r="I47">
-        <v>152.59200000000001</v>
+        <v>152.59399999999999</v>
       </c>
       <c r="J47">
         <v>152.59299999999999</v>
       </c>
       <c r="K47">
-        <v>152.834</v>
+        <v>152.83799999999999</v>
       </c>
       <c r="L47" s="1"/>
       <c r="M47" s="1" t="str">
@@ -7583,22 +7662,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S47" s="1"/>
-      <c r="T47" s="2">
+      <c r="S47" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U47" s="3">
+      <c r="T47" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C48" t="s">
         <v>4</v>
@@ -7607,25 +7685,25 @@
         <v>103</v>
       </c>
       <c r="E48">
-        <v>152.672</v>
+        <v>152.69800000000001</v>
       </c>
       <c r="F48">
-        <v>152.934</v>
+        <v>152.929</v>
       </c>
       <c r="G48">
-        <v>152.89500000000001</v>
+        <v>152.89400000000001</v>
       </c>
       <c r="H48">
-        <v>153.19999999999999</v>
+        <v>153.197</v>
       </c>
       <c r="I48">
-        <v>152.59299999999999</v>
+        <v>152.595</v>
       </c>
       <c r="J48">
         <v>152.59299999999999</v>
       </c>
       <c r="K48">
-        <v>152.83600000000001</v>
+        <v>152.839</v>
       </c>
       <c r="L48" s="1"/>
       <c r="M48" s="1" t="str">
@@ -7652,22 +7730,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S48" s="1"/>
-      <c r="T48" s="2">
+      <c r="S48" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U48" s="3">
+      <c r="T48" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C49" t="s">
         <v>4</v>
@@ -7676,25 +7753,25 @@
         <v>103</v>
       </c>
       <c r="E49">
-        <v>152.738</v>
+        <v>152.81299999999999</v>
       </c>
       <c r="F49">
-        <v>152.93199999999999</v>
+        <v>152.92699999999999</v>
       </c>
       <c r="G49">
-        <v>152.89500000000001</v>
+        <v>152.89400000000001</v>
       </c>
       <c r="H49">
-        <v>153.19900000000001</v>
+        <v>153.19499999999999</v>
       </c>
       <c r="I49">
-        <v>152.59399999999999</v>
+        <v>152.595</v>
       </c>
       <c r="J49">
-        <v>152.59299999999999</v>
+        <v>152.59200000000001</v>
       </c>
       <c r="K49">
-        <v>152.83799999999999</v>
+        <v>152.84100000000001</v>
       </c>
       <c r="L49" s="1"/>
       <c r="M49" s="1" t="str">
@@ -7721,22 +7798,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S49" s="1"/>
-      <c r="T49" s="2">
+      <c r="S49" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U49" s="3">
+      <c r="T49" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C50" t="s">
         <v>4</v>
@@ -7745,25 +7821,25 @@
         <v>103</v>
       </c>
       <c r="E50">
-        <v>152.69800000000001</v>
+        <v>152.81899999999999</v>
       </c>
       <c r="F50">
-        <v>152.929</v>
+        <v>152.92400000000001</v>
       </c>
       <c r="G50">
         <v>152.89400000000001</v>
       </c>
       <c r="H50">
-        <v>153.197</v>
+        <v>153.19399999999999</v>
       </c>
       <c r="I50">
-        <v>152.595</v>
+        <v>152.596</v>
       </c>
       <c r="J50">
-        <v>152.59299999999999</v>
+        <v>152.59200000000001</v>
       </c>
       <c r="K50">
-        <v>152.839</v>
+        <v>152.84200000000001</v>
       </c>
       <c r="L50" s="1"/>
       <c r="M50" s="1" t="str">
@@ -7790,22 +7866,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S50" s="1"/>
-      <c r="T50" s="2">
+      <c r="S50" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U50" s="3">
+      <c r="T50" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A51">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C51" t="s">
         <v>4</v>
@@ -7814,25 +7889,25 @@
         <v>103</v>
       </c>
       <c r="E51">
-        <v>152.81299999999999</v>
+        <v>152.816</v>
       </c>
       <c r="F51">
-        <v>152.92699999999999</v>
+        <v>152.922</v>
       </c>
       <c r="G51">
-        <v>152.89400000000001</v>
+        <v>152.893</v>
       </c>
       <c r="H51">
-        <v>153.19499999999999</v>
+        <v>153.19200000000001</v>
       </c>
       <c r="I51">
-        <v>152.595</v>
+        <v>152.59700000000001</v>
       </c>
       <c r="J51">
         <v>152.59200000000001</v>
       </c>
       <c r="K51">
-        <v>152.84100000000001</v>
+        <v>152.84399999999999</v>
       </c>
       <c r="L51" s="1"/>
       <c r="M51" s="1" t="str">
@@ -7859,22 +7934,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S51" s="1"/>
-      <c r="T51" s="2">
+      <c r="S51" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U51" s="3">
+      <c r="T51" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A52">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C52" t="s">
         <v>4</v>
@@ -7883,25 +7957,25 @@
         <v>103</v>
       </c>
       <c r="E52">
-        <v>152.81899999999999</v>
+        <v>152.82499999999999</v>
       </c>
       <c r="F52">
-        <v>152.92400000000001</v>
+        <v>152.91999999999999</v>
       </c>
       <c r="G52">
-        <v>152.89400000000001</v>
+        <v>152.893</v>
       </c>
       <c r="H52">
-        <v>153.19399999999999</v>
+        <v>153.191</v>
       </c>
       <c r="I52">
-        <v>152.596</v>
+        <v>152.59800000000001</v>
       </c>
       <c r="J52">
         <v>152.59200000000001</v>
       </c>
       <c r="K52">
-        <v>152.84200000000001</v>
+        <v>152.845</v>
       </c>
       <c r="L52" s="1"/>
       <c r="M52" s="1" t="str">
@@ -7928,22 +8002,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S52" s="1"/>
-      <c r="T52" s="2">
+      <c r="S52" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U52" s="3">
+      <c r="T52" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A53">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C53" t="s">
         <v>4</v>
@@ -7952,25 +8025,25 @@
         <v>103</v>
       </c>
       <c r="E53">
-        <v>152.816</v>
+        <v>152.75299999999999</v>
       </c>
       <c r="F53">
-        <v>152.922</v>
+        <v>152.917</v>
       </c>
       <c r="G53">
-        <v>152.893</v>
+        <v>152.892</v>
       </c>
       <c r="H53">
-        <v>153.19200000000001</v>
+        <v>153.18899999999999</v>
       </c>
       <c r="I53">
-        <v>152.59700000000001</v>
+        <v>152.59800000000001</v>
       </c>
       <c r="J53">
-        <v>152.59200000000001</v>
+        <v>152.59100000000001</v>
       </c>
       <c r="K53">
-        <v>152.84399999999999</v>
+        <v>152.84700000000001</v>
       </c>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="str">
@@ -7997,22 +8070,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S53" s="1"/>
-      <c r="T53" s="2">
+      <c r="S53" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U53" s="3">
+      <c r="T53" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A54">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C54" t="s">
         <v>4</v>
@@ -8021,25 +8093,25 @@
         <v>103</v>
       </c>
       <c r="E54">
-        <v>152.82499999999999</v>
+        <v>152.80600000000001</v>
       </c>
       <c r="F54">
-        <v>152.91999999999999</v>
+        <v>152.91499999999999</v>
       </c>
       <c r="G54">
-        <v>152.893</v>
+        <v>152.892</v>
       </c>
       <c r="H54">
-        <v>153.191</v>
+        <v>153.18700000000001</v>
       </c>
       <c r="I54">
-        <v>152.59800000000001</v>
+        <v>152.59899999999999</v>
       </c>
       <c r="J54">
-        <v>152.59200000000001</v>
+        <v>152.59100000000001</v>
       </c>
       <c r="K54">
-        <v>152.845</v>
+        <v>152.84899999999999</v>
       </c>
       <c r="L54" s="1"/>
       <c r="M54" s="1" t="str">
@@ -8066,22 +8138,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S54" s="1"/>
-      <c r="T54" s="2">
+      <c r="S54" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U54" s="3">
+      <c r="T54" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A55">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C55" t="s">
         <v>4</v>
@@ -8090,25 +8161,25 @@
         <v>103</v>
       </c>
       <c r="E55">
-        <v>152.75299999999999</v>
+        <v>152.78800000000001</v>
       </c>
       <c r="F55">
-        <v>152.917</v>
+        <v>152.91200000000001</v>
       </c>
       <c r="G55">
         <v>152.892</v>
       </c>
       <c r="H55">
-        <v>153.18899999999999</v>
+        <v>153.18600000000001</v>
       </c>
       <c r="I55">
-        <v>152.59800000000001</v>
+        <v>152.6</v>
       </c>
       <c r="J55">
         <v>152.59100000000001</v>
       </c>
       <c r="K55">
-        <v>152.84700000000001</v>
+        <v>152.85</v>
       </c>
       <c r="L55" s="1"/>
       <c r="M55" s="1" t="str">
@@ -8135,22 +8206,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S55" s="1"/>
-      <c r="T55" s="2">
+      <c r="S55" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U55" s="3">
+      <c r="T55" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A56">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C56" t="s">
         <v>4</v>
@@ -8159,25 +8229,25 @@
         <v>103</v>
       </c>
       <c r="E56">
-        <v>152.80600000000001</v>
+        <v>152.81399999999999</v>
       </c>
       <c r="F56">
-        <v>152.91499999999999</v>
+        <v>152.91</v>
       </c>
       <c r="G56">
-        <v>152.892</v>
+        <v>152.89099999999999</v>
       </c>
       <c r="H56">
-        <v>153.18700000000001</v>
+        <v>153.184</v>
       </c>
       <c r="I56">
-        <v>152.59899999999999</v>
+        <v>152.601</v>
       </c>
       <c r="J56">
         <v>152.59100000000001</v>
       </c>
       <c r="K56">
-        <v>152.84899999999999</v>
+        <v>152.852</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="str">
@@ -8204,22 +8274,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S56" s="1"/>
-      <c r="T56" s="2">
+      <c r="S56" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U56" s="3">
+      <c r="T56" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A57">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C57" t="s">
         <v>4</v>
@@ -8228,25 +8297,25 @@
         <v>103</v>
       </c>
       <c r="E57">
-        <v>152.78800000000001</v>
+        <v>152.803</v>
       </c>
       <c r="F57">
-        <v>152.91200000000001</v>
+        <v>152.90700000000001</v>
       </c>
       <c r="G57">
-        <v>152.892</v>
+        <v>152.89099999999999</v>
       </c>
       <c r="H57">
-        <v>153.18600000000001</v>
+        <v>153.18199999999999</v>
       </c>
       <c r="I57">
-        <v>152.6</v>
+        <v>152.601</v>
       </c>
       <c r="J57">
-        <v>152.59100000000001</v>
+        <v>152.59</v>
       </c>
       <c r="K57">
-        <v>152.85</v>
+        <v>152.85300000000001</v>
       </c>
       <c r="L57" s="1"/>
       <c r="M57" s="1" t="str">
@@ -8273,22 +8342,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S57" s="1"/>
-      <c r="T57" s="2">
+      <c r="S57" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U57" s="3">
+      <c r="T57" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A58">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C58" t="s">
         <v>4</v>
@@ -8297,25 +8365,25 @@
         <v>103</v>
       </c>
       <c r="E58">
-        <v>152.81399999999999</v>
+        <v>152.83799999999999</v>
       </c>
       <c r="F58">
-        <v>152.91</v>
+        <v>152.905</v>
       </c>
       <c r="G58">
         <v>152.89099999999999</v>
       </c>
       <c r="H58">
-        <v>153.184</v>
+        <v>153.18100000000001</v>
       </c>
       <c r="I58">
-        <v>152.601</v>
+        <v>152.602</v>
       </c>
       <c r="J58">
-        <v>152.59100000000001</v>
+        <v>152.59</v>
       </c>
       <c r="K58">
-        <v>152.852</v>
+        <v>152.85499999999999</v>
       </c>
       <c r="L58" s="1"/>
       <c r="M58" s="1" t="str">
@@ -8342,22 +8410,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S58" s="1"/>
-      <c r="T58" s="2">
+      <c r="S58" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U58" s="3">
+      <c r="T58" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A59">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C59" t="s">
         <v>4</v>
@@ -8366,25 +8433,25 @@
         <v>103</v>
       </c>
       <c r="E59">
-        <v>152.803</v>
+        <v>152.864</v>
       </c>
       <c r="F59">
-        <v>152.90700000000001</v>
+        <v>152.90299999999999</v>
       </c>
       <c r="G59">
-        <v>152.89099999999999</v>
+        <v>152.88999999999999</v>
       </c>
       <c r="H59">
-        <v>153.18199999999999</v>
+        <v>153.179</v>
       </c>
       <c r="I59">
-        <v>152.601</v>
+        <v>152.60300000000001</v>
       </c>
       <c r="J59">
         <v>152.59</v>
       </c>
       <c r="K59">
-        <v>152.85300000000001</v>
+        <v>152.857</v>
       </c>
       <c r="L59" s="1"/>
       <c r="M59" s="1" t="str">
@@ -8409,24 +8476,23 @@
       </c>
       <c r="R59" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>RES</v>
-      </c>
-      <c r="S59" s="1"/>
-      <c r="T59" s="2">
+        <v>SUP</v>
+      </c>
+      <c r="S59" s="2">
         <f t="shared" si="14"/>
-        <v>4</v>
-      </c>
-      <c r="U59" s="3">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A60">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C60" t="s">
         <v>4</v>
@@ -8435,25 +8501,25 @@
         <v>103</v>
       </c>
       <c r="E60">
-        <v>152.83799999999999</v>
+        <v>152.81299999999999</v>
       </c>
       <c r="F60">
-        <v>152.905</v>
+        <v>152.9</v>
       </c>
       <c r="G60">
-        <v>152.89099999999999</v>
+        <v>152.88999999999999</v>
       </c>
       <c r="H60">
-        <v>153.18100000000001</v>
+        <v>153.17699999999999</v>
       </c>
       <c r="I60">
-        <v>152.602</v>
+        <v>152.60400000000001</v>
       </c>
       <c r="J60">
         <v>152.59</v>
       </c>
       <c r="K60">
-        <v>152.85499999999999</v>
+        <v>152.858</v>
       </c>
       <c r="L60" s="1"/>
       <c r="M60" s="1" t="str">
@@ -8480,22 +8546,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S60" s="1"/>
-      <c r="T60" s="2">
+      <c r="S60" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U60" s="3">
+      <c r="T60" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A61">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C61" t="s">
         <v>4</v>
@@ -8504,25 +8569,25 @@
         <v>103</v>
       </c>
       <c r="E61">
-        <v>152.864</v>
+        <v>152.81200000000001</v>
       </c>
       <c r="F61">
-        <v>152.90299999999999</v>
+        <v>152.898</v>
       </c>
       <c r="G61">
-        <v>152.88999999999999</v>
+        <v>152.88900000000001</v>
       </c>
       <c r="H61">
-        <v>153.179</v>
+        <v>153.17599999999999</v>
       </c>
       <c r="I61">
-        <v>152.60300000000001</v>
+        <v>152.60400000000001</v>
       </c>
       <c r="J61">
         <v>152.59</v>
       </c>
       <c r="K61">
-        <v>152.857</v>
+        <v>152.86000000000001</v>
       </c>
       <c r="L61" s="1"/>
       <c r="M61" s="1" t="str">
@@ -8547,24 +8612,23 @@
       </c>
       <c r="R61" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>SUP</v>
-      </c>
-      <c r="S61" s="1"/>
-      <c r="T61" s="2">
+        <v>RES</v>
+      </c>
+      <c r="S61" s="2">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="U61" s="3">
+        <v>4</v>
+      </c>
+      <c r="T61" s="3">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A62">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C62" t="s">
         <v>4</v>
@@ -8573,25 +8637,25 @@
         <v>103</v>
       </c>
       <c r="E62">
-        <v>152.81299999999999</v>
+        <v>152.84700000000001</v>
       </c>
       <c r="F62">
-        <v>152.9</v>
+        <v>152.89500000000001</v>
       </c>
       <c r="G62">
-        <v>152.88999999999999</v>
+        <v>152.88900000000001</v>
       </c>
       <c r="H62">
-        <v>153.17699999999999</v>
+        <v>153.17400000000001</v>
       </c>
       <c r="I62">
-        <v>152.60400000000001</v>
+        <v>152.60499999999999</v>
       </c>
       <c r="J62">
-        <v>152.59</v>
+        <v>152.589</v>
       </c>
       <c r="K62">
-        <v>152.858</v>
+        <v>152.86099999999999</v>
       </c>
       <c r="L62" s="1"/>
       <c r="M62" s="1" t="str">
@@ -8618,22 +8682,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S62" s="1"/>
-      <c r="T62" s="2">
+      <c r="S62" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U62" s="3">
+      <c r="T62" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A63">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C63" t="s">
         <v>4</v>
@@ -8642,25 +8705,25 @@
         <v>103</v>
       </c>
       <c r="E63">
-        <v>152.81200000000001</v>
+        <v>152.803</v>
       </c>
       <c r="F63">
-        <v>152.898</v>
+        <v>152.893</v>
       </c>
       <c r="G63">
         <v>152.88900000000001</v>
       </c>
       <c r="H63">
-        <v>153.17599999999999</v>
+        <v>153.173</v>
       </c>
       <c r="I63">
-        <v>152.60400000000001</v>
+        <v>152.60599999999999</v>
       </c>
       <c r="J63">
-        <v>152.59</v>
+        <v>152.589</v>
       </c>
       <c r="K63">
-        <v>152.86000000000001</v>
+        <v>152.863</v>
       </c>
       <c r="L63" s="1"/>
       <c r="M63" s="1" t="str">
@@ -8687,22 +8750,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S63" s="1"/>
-      <c r="T63" s="2">
+      <c r="S63" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U63" s="3">
+      <c r="T63" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A64">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C64" t="s">
         <v>4</v>
@@ -8711,25 +8773,25 @@
         <v>103</v>
       </c>
       <c r="E64">
-        <v>152.84700000000001</v>
+        <v>152.84</v>
       </c>
       <c r="F64">
-        <v>152.89500000000001</v>
+        <v>152.88999999999999</v>
       </c>
       <c r="G64">
-        <v>152.88900000000001</v>
+        <v>152.88800000000001</v>
       </c>
       <c r="H64">
-        <v>153.17400000000001</v>
+        <v>153.17099999999999</v>
       </c>
       <c r="I64">
-        <v>152.60499999999999</v>
+        <v>152.607</v>
       </c>
       <c r="J64">
         <v>152.589</v>
       </c>
       <c r="K64">
-        <v>152.86099999999999</v>
+        <v>152.864</v>
       </c>
       <c r="L64" s="1"/>
       <c r="M64" s="1" t="str">
@@ -8756,22 +8818,21 @@
         <f t="shared" si="13"/>
         <v>RES</v>
       </c>
-      <c r="S64" s="1"/>
-      <c r="T64" s="2">
+      <c r="S64" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="U64" s="3">
+      <c r="T64" s="3">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A65">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C65" t="s">
         <v>4</v>
@@ -8780,25 +8841,25 @@
         <v>103</v>
       </c>
       <c r="E65">
-        <v>152.803</v>
+        <v>152.874</v>
       </c>
       <c r="F65">
-        <v>152.893</v>
+        <v>152.88800000000001</v>
       </c>
       <c r="G65">
-        <v>152.88900000000001</v>
+        <v>152.88800000000001</v>
       </c>
       <c r="H65">
-        <v>153.173</v>
+        <v>153.16900000000001</v>
       </c>
       <c r="I65">
-        <v>152.60599999999999</v>
+        <v>152.608</v>
       </c>
       <c r="J65">
         <v>152.589</v>
       </c>
       <c r="K65">
-        <v>152.863</v>
+        <v>152.86600000000001</v>
       </c>
       <c r="L65" s="1"/>
       <c r="M65" s="1" t="str">
@@ -8823,162 +8884,159 @@
       </c>
       <c r="R65" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>RES</v>
-      </c>
-      <c r="S65" s="1"/>
-      <c r="T65" s="2">
+        <v>SUP</v>
+      </c>
+      <c r="S65" s="2">
         <f t="shared" si="14"/>
-        <v>4</v>
-      </c>
-      <c r="U65" s="3">
+        <v>3</v>
+      </c>
+      <c r="T65" s="3">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="4">
+        <v>64</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E66" s="4">
+        <v>152.83099999999999</v>
+      </c>
+      <c r="F66" s="4">
+        <v>152.886</v>
+      </c>
+      <c r="G66" s="4">
+        <v>152.88800000000001</v>
+      </c>
+      <c r="H66" s="4">
+        <v>153.16800000000001</v>
+      </c>
+      <c r="I66" s="4">
+        <v>152.608</v>
+      </c>
+      <c r="J66" s="4">
+        <v>152.58799999999999</v>
+      </c>
+      <c r="K66" s="4">
+        <v>152.86799999999999</v>
+      </c>
+      <c r="L66" s="5"/>
+      <c r="M66" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>RES</v>
+      </c>
+      <c r="N66" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>RES</v>
+      </c>
+      <c r="O66" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>RES</v>
+      </c>
+      <c r="P66" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>SUP</v>
+      </c>
+      <c r="Q66" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>SUP</v>
+      </c>
+      <c r="R66" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>RES</v>
+      </c>
+      <c r="S66" s="6">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="T66" s="7">
         <f t="shared" si="15"/>
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66">
-        <v>62</v>
-      </c>
-      <c r="B66" t="s">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="4">
         <v>65</v>
       </c>
-      <c r="C66" t="s">
-        <v>4</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="B67" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E66">
-        <v>152.84</v>
-      </c>
-      <c r="F66">
-        <v>152.88999999999999</v>
-      </c>
-      <c r="G66">
-        <v>152.88800000000001</v>
-      </c>
-      <c r="H66">
-        <v>153.17099999999999</v>
-      </c>
-      <c r="I66">
-        <v>152.607</v>
-      </c>
-      <c r="J66">
-        <v>152.589</v>
-      </c>
-      <c r="K66">
-        <v>152.864</v>
-      </c>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>RES</v>
-      </c>
-      <c r="N66" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>RES</v>
-      </c>
-      <c r="O66" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>RES</v>
-      </c>
-      <c r="P66" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v>SUP</v>
-      </c>
-      <c r="Q66" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v>SUP</v>
-      </c>
-      <c r="R66" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>RES</v>
-      </c>
-      <c r="S66" s="1"/>
-      <c r="T66" s="2">
-        <f t="shared" si="14"/>
-        <v>4</v>
-      </c>
-      <c r="U66" s="3">
-        <f t="shared" si="15"/>
+      <c r="E67" s="4">
+        <v>152.84399999999999</v>
+      </c>
+      <c r="F67" s="4">
+        <v>152.88300000000001</v>
+      </c>
+      <c r="G67" s="4">
+        <v>152.887</v>
+      </c>
+      <c r="H67" s="4">
+        <v>153.166</v>
+      </c>
+      <c r="I67" s="4">
+        <v>152.60900000000001</v>
+      </c>
+      <c r="J67" s="4">
+        <v>152.58799999999999</v>
+      </c>
+      <c r="K67" s="4">
+        <v>152.869</v>
+      </c>
+      <c r="L67" s="5"/>
+      <c r="M67" s="5" t="str">
+        <f t="shared" ref="M67:M101" si="16">IF($E67&gt;F67,"SUP","RES")</f>
+        <v>RES</v>
+      </c>
+      <c r="N67" s="5" t="str">
+        <f t="shared" ref="N67:N101" si="17">IF($E67&gt;G67,"SUP","RES")</f>
+        <v>RES</v>
+      </c>
+      <c r="O67" s="5" t="str">
+        <f t="shared" ref="O67:O101" si="18">IF($E67&gt;H67,"SUP","RES")</f>
+        <v>RES</v>
+      </c>
+      <c r="P67" s="5" t="str">
+        <f t="shared" ref="P67:P101" si="19">IF($E67&gt;I67,"SUP","RES")</f>
+        <v>SUP</v>
+      </c>
+      <c r="Q67" s="5" t="str">
+        <f t="shared" ref="Q67:Q101" si="20">IF($E67&gt;J67,"SUP","RES")</f>
+        <v>SUP</v>
+      </c>
+      <c r="R67" s="5" t="str">
+        <f t="shared" ref="R67:R101" si="21">IF($E67&gt;K67,"SUP","RES")</f>
+        <v>RES</v>
+      </c>
+      <c r="S67" s="6">
+        <f t="shared" ref="S67:S101" si="22">COUNTIF(M67:R67,"RES")</f>
+        <v>4</v>
+      </c>
+      <c r="T67" s="7">
+        <f t="shared" ref="T67:T101" si="23">COUNTIF(M67:R67,"SUP")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67">
-        <v>63</v>
-      </c>
-      <c r="B67" t="s">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="4">
         <v>66</v>
       </c>
-      <c r="C67" t="s">
-        <v>4</v>
-      </c>
-      <c r="D67" t="s">
-        <v>103</v>
-      </c>
-      <c r="E67">
-        <v>152.874</v>
-      </c>
-      <c r="F67">
-        <v>152.88800000000001</v>
-      </c>
-      <c r="G67">
-        <v>152.88800000000001</v>
-      </c>
-      <c r="H67">
-        <v>153.16900000000001</v>
-      </c>
-      <c r="I67">
-        <v>152.608</v>
-      </c>
-      <c r="J67">
-        <v>152.589</v>
-      </c>
-      <c r="K67">
-        <v>152.86600000000001</v>
-      </c>
-      <c r="L67" s="1"/>
-      <c r="M67" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>RES</v>
-      </c>
-      <c r="N67" s="1" t="str">
-        <f t="shared" si="9"/>
-        <v>RES</v>
-      </c>
-      <c r="O67" s="1" t="str">
-        <f t="shared" si="10"/>
-        <v>RES</v>
-      </c>
-      <c r="P67" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v>SUP</v>
-      </c>
-      <c r="Q67" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v>SUP</v>
-      </c>
-      <c r="R67" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v>SUP</v>
-      </c>
-      <c r="S67" s="1"/>
-      <c r="T67" s="2">
-        <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="U67" s="3">
-        <f t="shared" si="15"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="4">
-        <v>64</v>
-      </c>
       <c r="B68" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>4</v>
@@ -8987,205 +9045,202 @@
         <v>103</v>
       </c>
       <c r="E68" s="4">
-        <v>152.83099999999999</v>
+        <v>152.81</v>
       </c>
       <c r="F68" s="4">
-        <v>152.886</v>
+        <v>152.881</v>
       </c>
       <c r="G68" s="4">
-        <v>152.88800000000001</v>
+        <v>152.887</v>
       </c>
       <c r="H68" s="4">
-        <v>153.16800000000001</v>
+        <v>153.16399999999999</v>
       </c>
       <c r="I68" s="4">
-        <v>152.608</v>
+        <v>152.61000000000001</v>
       </c>
       <c r="J68" s="4">
         <v>152.58799999999999</v>
       </c>
       <c r="K68" s="4">
-        <v>152.86799999999999</v>
+        <v>152.87100000000001</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v>RES</v>
       </c>
       <c r="N68" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>RES</v>
       </c>
       <c r="O68" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v>RES</v>
       </c>
       <c r="P68" s="5" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>SUP</v>
       </c>
       <c r="Q68" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>SUP</v>
       </c>
       <c r="R68" s="5" t="str">
-        <f t="shared" si="13"/>
-        <v>RES</v>
-      </c>
-      <c r="S68" s="5"/>
-      <c r="T68" s="6">
-        <f t="shared" si="14"/>
-        <v>4</v>
-      </c>
-      <c r="U68" s="7">
-        <f t="shared" si="15"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="4">
-        <v>65</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E69" s="4">
-        <v>152.84399999999999</v>
-      </c>
-      <c r="F69" s="4">
-        <v>152.88300000000001</v>
-      </c>
-      <c r="G69" s="4">
-        <v>152.887</v>
-      </c>
-      <c r="H69" s="4">
-        <v>153.166</v>
-      </c>
-      <c r="I69" s="4">
-        <v>152.60900000000001</v>
-      </c>
-      <c r="J69" s="4">
-        <v>152.58799999999999</v>
-      </c>
-      <c r="K69" s="4">
-        <v>152.869</v>
-      </c>
-      <c r="L69" s="5"/>
-      <c r="M69" s="5" t="str">
-        <f t="shared" ref="M69:M103" si="16">IF($E69&gt;F69,"SUP","RES")</f>
-        <v>RES</v>
-      </c>
-      <c r="N69" s="5" t="str">
-        <f t="shared" ref="N69:N103" si="17">IF($E69&gt;G69,"SUP","RES")</f>
-        <v>RES</v>
-      </c>
-      <c r="O69" s="5" t="str">
-        <f t="shared" ref="O69:O103" si="18">IF($E69&gt;H69,"SUP","RES")</f>
-        <v>RES</v>
-      </c>
-      <c r="P69" s="5" t="str">
-        <f t="shared" ref="P69:P103" si="19">IF($E69&gt;I69,"SUP","RES")</f>
-        <v>SUP</v>
-      </c>
-      <c r="Q69" s="5" t="str">
-        <f t="shared" ref="Q69:Q103" si="20">IF($E69&gt;J69,"SUP","RES")</f>
-        <v>SUP</v>
-      </c>
-      <c r="R69" s="5" t="str">
-        <f t="shared" ref="R69:R103" si="21">IF($E69&gt;K69,"SUP","RES")</f>
-        <v>RES</v>
-      </c>
-      <c r="S69" s="5"/>
-      <c r="T69" s="6">
-        <f t="shared" ref="T69:T103" si="22">COUNTIF(M69:R69,"RES")</f>
-        <v>4</v>
-      </c>
-      <c r="U69" s="7">
-        <f t="shared" ref="U69:U103" si="23">COUNTIF(M69:R69,"SUP")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="4">
-        <v>66</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E70" s="4">
-        <v>152.81</v>
-      </c>
-      <c r="F70" s="4">
-        <v>152.881</v>
-      </c>
-      <c r="G70" s="4">
-        <v>152.887</v>
-      </c>
-      <c r="H70" s="4">
-        <v>153.16399999999999</v>
-      </c>
-      <c r="I70" s="4">
-        <v>152.61000000000001</v>
-      </c>
-      <c r="J70" s="4">
-        <v>152.58799999999999</v>
-      </c>
-      <c r="K70" s="4">
-        <v>152.87100000000001</v>
-      </c>
-      <c r="L70" s="5"/>
-      <c r="M70" s="5" t="str">
-        <f t="shared" si="16"/>
-        <v>RES</v>
-      </c>
-      <c r="N70" s="5" t="str">
-        <f t="shared" si="17"/>
-        <v>RES</v>
-      </c>
-      <c r="O70" s="5" t="str">
-        <f t="shared" si="18"/>
-        <v>RES</v>
-      </c>
-      <c r="P70" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>SUP</v>
-      </c>
-      <c r="Q70" s="5" t="str">
-        <f t="shared" si="20"/>
-        <v>SUP</v>
-      </c>
-      <c r="R70" s="5" t="str">
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S70" s="5"/>
-      <c r="T70" s="6">
+      <c r="S68" s="6">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U70" s="7">
+      <c r="T68" s="7">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>70</v>
+      </c>
+      <c r="C69" t="s">
+        <v>4</v>
+      </c>
+      <c r="D69" t="s">
+        <v>103</v>
+      </c>
+      <c r="E69">
+        <v>152.809</v>
+      </c>
+      <c r="F69">
+        <v>152.87799999999999</v>
+      </c>
+      <c r="G69">
+        <v>152.887</v>
+      </c>
+      <c r="H69">
+        <v>153.16300000000001</v>
+      </c>
+      <c r="I69">
+        <v>152.61099999999999</v>
+      </c>
+      <c r="J69">
+        <v>152.58799999999999</v>
+      </c>
+      <c r="K69">
+        <v>152.87200000000001</v>
+      </c>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>RES</v>
+      </c>
+      <c r="N69" s="1" t="str">
+        <f t="shared" si="17"/>
+        <v>RES</v>
+      </c>
+      <c r="O69" s="1" t="str">
+        <f t="shared" si="18"/>
+        <v>RES</v>
+      </c>
+      <c r="P69" s="1" t="str">
+        <f t="shared" si="19"/>
+        <v>SUP</v>
+      </c>
+      <c r="Q69" s="1" t="str">
+        <f t="shared" si="20"/>
+        <v>SUP</v>
+      </c>
+      <c r="R69" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>RES</v>
+      </c>
+      <c r="S69" s="2">
+        <f t="shared" si="22"/>
+        <v>4</v>
+      </c>
+      <c r="T69" s="3">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="B70" t="s">
+        <v>71</v>
+      </c>
+      <c r="C70" t="s">
+        <v>4</v>
+      </c>
+      <c r="D70" t="s">
+        <v>103</v>
+      </c>
+      <c r="E70">
+        <v>152.81299999999999</v>
+      </c>
+      <c r="F70">
+        <v>152.876</v>
+      </c>
+      <c r="G70">
+        <v>152.886</v>
+      </c>
+      <c r="H70">
+        <v>153.161</v>
+      </c>
+      <c r="I70">
+        <v>152.61099999999999</v>
+      </c>
+      <c r="J70">
+        <v>152.58699999999999</v>
+      </c>
+      <c r="K70">
+        <v>152.874</v>
+      </c>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v>RES</v>
+      </c>
+      <c r="N70" s="1" t="str">
+        <f t="shared" si="17"/>
+        <v>RES</v>
+      </c>
+      <c r="O70" s="1" t="str">
+        <f t="shared" si="18"/>
+        <v>RES</v>
+      </c>
+      <c r="P70" s="1" t="str">
+        <f t="shared" si="19"/>
+        <v>SUP</v>
+      </c>
+      <c r="Q70" s="1" t="str">
+        <f t="shared" si="20"/>
+        <v>SUP</v>
+      </c>
+      <c r="R70" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>RES</v>
+      </c>
+      <c r="S70" s="2">
+        <f t="shared" si="22"/>
+        <v>4</v>
+      </c>
+      <c r="T70" s="3">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A71">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C71" t="s">
         <v>4</v>
@@ -9194,25 +9249,25 @@
         <v>103</v>
       </c>
       <c r="E71">
-        <v>152.809</v>
+        <v>152.779</v>
       </c>
       <c r="F71">
-        <v>152.87799999999999</v>
+        <v>152.87299999999999</v>
       </c>
       <c r="G71">
-        <v>152.887</v>
+        <v>152.886</v>
       </c>
       <c r="H71">
-        <v>153.16300000000001</v>
+        <v>153.15899999999999</v>
       </c>
       <c r="I71">
-        <v>152.61099999999999</v>
+        <v>152.61199999999999</v>
       </c>
       <c r="J71">
-        <v>152.58799999999999</v>
+        <v>152.58699999999999</v>
       </c>
       <c r="K71">
-        <v>152.87200000000001</v>
+        <v>152.876</v>
       </c>
       <c r="L71" s="1"/>
       <c r="M71" s="1" t="str">
@@ -9239,22 +9294,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S71" s="1"/>
-      <c r="T71" s="2">
+      <c r="S71" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U71" s="3">
+      <c r="T71" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A72">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C72" t="s">
         <v>4</v>
@@ -9263,25 +9317,25 @@
         <v>103</v>
       </c>
       <c r="E72">
-        <v>152.81299999999999</v>
+        <v>152.76900000000001</v>
       </c>
       <c r="F72">
-        <v>152.876</v>
+        <v>152.87100000000001</v>
       </c>
       <c r="G72">
-        <v>152.886</v>
+        <v>152.88499999999999</v>
       </c>
       <c r="H72">
-        <v>153.161</v>
+        <v>153.15799999999999</v>
       </c>
       <c r="I72">
-        <v>152.61099999999999</v>
+        <v>152.613</v>
       </c>
       <c r="J72">
         <v>152.58699999999999</v>
       </c>
       <c r="K72">
-        <v>152.874</v>
+        <v>152.87700000000001</v>
       </c>
       <c r="L72" s="1"/>
       <c r="M72" s="1" t="str">
@@ -9308,22 +9362,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S72" s="1"/>
-      <c r="T72" s="2">
+      <c r="S72" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U72" s="3">
+      <c r="T72" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A73">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C73" t="s">
         <v>4</v>
@@ -9332,25 +9385,25 @@
         <v>103</v>
       </c>
       <c r="E73">
-        <v>152.779</v>
+        <v>152.74299999999999</v>
       </c>
       <c r="F73">
-        <v>152.87299999999999</v>
+        <v>152.869</v>
       </c>
       <c r="G73">
-        <v>152.886</v>
+        <v>152.88499999999999</v>
       </c>
       <c r="H73">
-        <v>153.15899999999999</v>
+        <v>153.15600000000001</v>
       </c>
       <c r="I73">
-        <v>152.61199999999999</v>
+        <v>152.614</v>
       </c>
       <c r="J73">
         <v>152.58699999999999</v>
       </c>
       <c r="K73">
-        <v>152.876</v>
+        <v>152.87899999999999</v>
       </c>
       <c r="L73" s="1"/>
       <c r="M73" s="1" t="str">
@@ -9377,22 +9430,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S73" s="1"/>
-      <c r="T73" s="2">
+      <c r="S73" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U73" s="3">
+      <c r="T73" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A74">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C74" t="s">
         <v>4</v>
@@ -9401,25 +9453,25 @@
         <v>103</v>
       </c>
       <c r="E74">
-        <v>152.76900000000001</v>
+        <v>152.75399999999999</v>
       </c>
       <c r="F74">
-        <v>152.87100000000001</v>
+        <v>152.86600000000001</v>
       </c>
       <c r="G74">
         <v>152.88499999999999</v>
       </c>
       <c r="H74">
-        <v>153.15799999999999</v>
+        <v>153.154</v>
       </c>
       <c r="I74">
-        <v>152.613</v>
+        <v>152.614</v>
       </c>
       <c r="J74">
         <v>152.58699999999999</v>
       </c>
       <c r="K74">
-        <v>152.87700000000001</v>
+        <v>152.88</v>
       </c>
       <c r="L74" s="1"/>
       <c r="M74" s="1" t="str">
@@ -9446,22 +9498,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S74" s="1"/>
-      <c r="T74" s="2">
+      <c r="S74" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U74" s="3">
+      <c r="T74" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A75">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C75" t="s">
         <v>4</v>
@@ -9470,25 +9521,25 @@
         <v>103</v>
       </c>
       <c r="E75">
-        <v>152.74299999999999</v>
+        <v>152.73599999999999</v>
       </c>
       <c r="F75">
-        <v>152.869</v>
+        <v>152.864</v>
       </c>
       <c r="G75">
-        <v>152.88499999999999</v>
+        <v>152.88399999999999</v>
       </c>
       <c r="H75">
-        <v>153.15600000000001</v>
+        <v>153.15299999999999</v>
       </c>
       <c r="I75">
-        <v>152.614</v>
+        <v>152.61500000000001</v>
       </c>
       <c r="J75">
-        <v>152.58699999999999</v>
+        <v>152.58600000000001</v>
       </c>
       <c r="K75">
-        <v>152.87899999999999</v>
+        <v>152.88200000000001</v>
       </c>
       <c r="L75" s="1"/>
       <c r="M75" s="1" t="str">
@@ -9515,22 +9566,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S75" s="1"/>
-      <c r="T75" s="2">
+      <c r="S75" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U75" s="3">
+      <c r="T75" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A76">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C76" t="s">
         <v>4</v>
@@ -9539,25 +9589,25 @@
         <v>103</v>
       </c>
       <c r="E76">
-        <v>152.75399999999999</v>
+        <v>152.76300000000001</v>
       </c>
       <c r="F76">
-        <v>152.86600000000001</v>
+        <v>152.86099999999999</v>
       </c>
       <c r="G76">
-        <v>152.88499999999999</v>
+        <v>152.88399999999999</v>
       </c>
       <c r="H76">
-        <v>153.154</v>
+        <v>153.15100000000001</v>
       </c>
       <c r="I76">
-        <v>152.614</v>
+        <v>152.61600000000001</v>
       </c>
       <c r="J76">
-        <v>152.58699999999999</v>
+        <v>152.58600000000001</v>
       </c>
       <c r="K76">
-        <v>152.88</v>
+        <v>152.88300000000001</v>
       </c>
       <c r="L76" s="1"/>
       <c r="M76" s="1" t="str">
@@ -9584,22 +9634,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S76" s="1"/>
-      <c r="T76" s="2">
+      <c r="S76" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U76" s="3">
+      <c r="T76" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A77">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C77" t="s">
         <v>4</v>
@@ -9608,25 +9657,25 @@
         <v>103</v>
       </c>
       <c r="E77">
-        <v>152.73599999999999</v>
+        <v>152.77000000000001</v>
       </c>
       <c r="F77">
-        <v>152.864</v>
+        <v>152.85900000000001</v>
       </c>
       <c r="G77">
         <v>152.88399999999999</v>
       </c>
       <c r="H77">
-        <v>153.15299999999999</v>
+        <v>153.15</v>
       </c>
       <c r="I77">
-        <v>152.61500000000001</v>
+        <v>152.61699999999999</v>
       </c>
       <c r="J77">
         <v>152.58600000000001</v>
       </c>
       <c r="K77">
-        <v>152.88200000000001</v>
+        <v>152.88499999999999</v>
       </c>
       <c r="L77" s="1"/>
       <c r="M77" s="1" t="str">
@@ -9653,22 +9702,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S77" s="1"/>
-      <c r="T77" s="2">
+      <c r="S77" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U77" s="3">
+      <c r="T77" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A78">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C78" t="s">
         <v>4</v>
@@ -9677,25 +9725,25 @@
         <v>103</v>
       </c>
       <c r="E78">
-        <v>152.76300000000001</v>
+        <v>152.77699999999999</v>
       </c>
       <c r="F78">
-        <v>152.86099999999999</v>
+        <v>152.85599999999999</v>
       </c>
       <c r="G78">
-        <v>152.88399999999999</v>
+        <v>152.88300000000001</v>
       </c>
       <c r="H78">
-        <v>153.15100000000001</v>
+        <v>153.148</v>
       </c>
       <c r="I78">
-        <v>152.61600000000001</v>
+        <v>152.61699999999999</v>
       </c>
       <c r="J78">
         <v>152.58600000000001</v>
       </c>
       <c r="K78">
-        <v>152.88300000000001</v>
+        <v>152.887</v>
       </c>
       <c r="L78" s="1"/>
       <c r="M78" s="1" t="str">
@@ -9722,22 +9770,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S78" s="1"/>
-      <c r="T78" s="2">
+      <c r="S78" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U78" s="3">
+      <c r="T78" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A79">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C79" t="s">
         <v>4</v>
@@ -9746,25 +9793,25 @@
         <v>103</v>
       </c>
       <c r="E79">
-        <v>152.77000000000001</v>
+        <v>152.80099999999999</v>
       </c>
       <c r="F79">
-        <v>152.85900000000001</v>
+        <v>152.85400000000001</v>
       </c>
       <c r="G79">
-        <v>152.88399999999999</v>
+        <v>152.88300000000001</v>
       </c>
       <c r="H79">
-        <v>153.15</v>
+        <v>153.14599999999999</v>
       </c>
       <c r="I79">
-        <v>152.61699999999999</v>
+        <v>152.61799999999999</v>
       </c>
       <c r="J79">
-        <v>152.58600000000001</v>
+        <v>152.58500000000001</v>
       </c>
       <c r="K79">
-        <v>152.88499999999999</v>
+        <v>152.88800000000001</v>
       </c>
       <c r="L79" s="1"/>
       <c r="M79" s="1" t="str">
@@ -9791,22 +9838,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S79" s="1"/>
-      <c r="T79" s="2">
+      <c r="S79" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U79" s="3">
+      <c r="T79" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A80">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C80" t="s">
         <v>4</v>
@@ -9815,25 +9861,25 @@
         <v>103</v>
       </c>
       <c r="E80">
-        <v>152.77699999999999</v>
+        <v>152.81200000000001</v>
       </c>
       <c r="F80">
-        <v>152.85599999999999</v>
+        <v>152.852</v>
       </c>
       <c r="G80">
-        <v>152.88300000000001</v>
+        <v>152.88200000000001</v>
       </c>
       <c r="H80">
-        <v>153.148</v>
+        <v>153.14500000000001</v>
       </c>
       <c r="I80">
-        <v>152.61699999999999</v>
+        <v>152.619</v>
       </c>
       <c r="J80">
-        <v>152.58600000000001</v>
+        <v>152.58500000000001</v>
       </c>
       <c r="K80">
-        <v>152.887</v>
+        <v>152.88999999999999</v>
       </c>
       <c r="L80" s="1"/>
       <c r="M80" s="1" t="str">
@@ -9860,22 +9906,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S80" s="1"/>
-      <c r="T80" s="2">
+      <c r="S80" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U80" s="3">
+      <c r="T80" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A81">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C81" t="s">
         <v>4</v>
@@ -9884,25 +9929,25 @@
         <v>103</v>
       </c>
       <c r="E81">
-        <v>152.80099999999999</v>
+        <v>152.786</v>
       </c>
       <c r="F81">
-        <v>152.85400000000001</v>
+        <v>152.84899999999999</v>
       </c>
       <c r="G81">
-        <v>152.88300000000001</v>
+        <v>152.88200000000001</v>
       </c>
       <c r="H81">
-        <v>153.14599999999999</v>
+        <v>153.143</v>
       </c>
       <c r="I81">
-        <v>152.61799999999999</v>
+        <v>152.62</v>
       </c>
       <c r="J81">
         <v>152.58500000000001</v>
       </c>
       <c r="K81">
-        <v>152.88800000000001</v>
+        <v>152.89099999999999</v>
       </c>
       <c r="L81" s="1"/>
       <c r="M81" s="1" t="str">
@@ -9929,22 +9974,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S81" s="1"/>
-      <c r="T81" s="2">
+      <c r="S81" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U81" s="3">
+      <c r="T81" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A82">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C82" t="s">
         <v>4</v>
@@ -9953,25 +9997,25 @@
         <v>103</v>
       </c>
       <c r="E82">
-        <v>152.81200000000001</v>
+        <v>152.81399999999999</v>
       </c>
       <c r="F82">
-        <v>152.852</v>
+        <v>152.84700000000001</v>
       </c>
       <c r="G82">
         <v>152.88200000000001</v>
       </c>
       <c r="H82">
-        <v>153.14500000000001</v>
+        <v>153.14099999999999</v>
       </c>
       <c r="I82">
-        <v>152.619</v>
+        <v>152.62100000000001</v>
       </c>
       <c r="J82">
         <v>152.58500000000001</v>
       </c>
       <c r="K82">
-        <v>152.88999999999999</v>
+        <v>152.893</v>
       </c>
       <c r="L82" s="1"/>
       <c r="M82" s="1" t="str">
@@ -9998,22 +10042,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S82" s="1"/>
-      <c r="T82" s="2">
+      <c r="S82" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U82" s="3">
+      <c r="T82" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A83">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C83" t="s">
         <v>4</v>
@@ -10022,25 +10065,25 @@
         <v>103</v>
       </c>
       <c r="E83">
-        <v>152.786</v>
+        <v>152.78700000000001</v>
       </c>
       <c r="F83">
-        <v>152.84899999999999</v>
+        <v>152.84399999999999</v>
       </c>
       <c r="G83">
-        <v>152.88200000000001</v>
+        <v>152.881</v>
       </c>
       <c r="H83">
-        <v>153.143</v>
+        <v>153.13999999999999</v>
       </c>
       <c r="I83">
-        <v>152.62</v>
+        <v>152.62100000000001</v>
       </c>
       <c r="J83">
-        <v>152.58500000000001</v>
+        <v>152.584</v>
       </c>
       <c r="K83">
-        <v>152.89099999999999</v>
+        <v>152.89400000000001</v>
       </c>
       <c r="L83" s="1"/>
       <c r="M83" s="1" t="str">
@@ -10067,22 +10110,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S83" s="1"/>
-      <c r="T83" s="2">
+      <c r="S83" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U83" s="3">
+      <c r="T83" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A84">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C84" t="s">
         <v>4</v>
@@ -10091,25 +10133,25 @@
         <v>103</v>
       </c>
       <c r="E84">
-        <v>152.81399999999999</v>
+        <v>152.72999999999999</v>
       </c>
       <c r="F84">
-        <v>152.84700000000001</v>
+        <v>152.84200000000001</v>
       </c>
       <c r="G84">
-        <v>152.88200000000001</v>
+        <v>152.881</v>
       </c>
       <c r="H84">
-        <v>153.14099999999999</v>
+        <v>153.13800000000001</v>
       </c>
       <c r="I84">
-        <v>152.62100000000001</v>
+        <v>152.62200000000001</v>
       </c>
       <c r="J84">
-        <v>152.58500000000001</v>
+        <v>152.584</v>
       </c>
       <c r="K84">
-        <v>152.893</v>
+        <v>152.89599999999999</v>
       </c>
       <c r="L84" s="1"/>
       <c r="M84" s="1" t="str">
@@ -10136,22 +10178,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S84" s="1"/>
-      <c r="T84" s="2">
+      <c r="S84" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U84" s="3">
+      <c r="T84" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A85">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
         <v>4</v>
@@ -10160,25 +10201,25 @@
         <v>103</v>
       </c>
       <c r="E85">
-        <v>152.78700000000001</v>
+        <v>152.72800000000001</v>
       </c>
       <c r="F85">
-        <v>152.84399999999999</v>
+        <v>152.84</v>
       </c>
       <c r="G85">
         <v>152.881</v>
       </c>
       <c r="H85">
-        <v>153.13999999999999</v>
+        <v>153.136</v>
       </c>
       <c r="I85">
-        <v>152.62100000000001</v>
+        <v>152.62299999999999</v>
       </c>
       <c r="J85">
         <v>152.584</v>
       </c>
       <c r="K85">
-        <v>152.89400000000001</v>
+        <v>152.898</v>
       </c>
       <c r="L85" s="1"/>
       <c r="M85" s="1" t="str">
@@ -10205,22 +10246,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S85" s="1"/>
-      <c r="T85" s="2">
+      <c r="S85" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U85" s="3">
+      <c r="T85" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A86">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C86" t="s">
         <v>4</v>
@@ -10229,25 +10269,25 @@
         <v>103</v>
       </c>
       <c r="E86">
-        <v>152.72999999999999</v>
+        <v>152.72900000000001</v>
       </c>
       <c r="F86">
-        <v>152.84200000000001</v>
+        <v>152.83699999999999</v>
       </c>
       <c r="G86">
-        <v>152.881</v>
+        <v>152.88</v>
       </c>
       <c r="H86">
-        <v>153.13800000000001</v>
+        <v>153.13499999999999</v>
       </c>
       <c r="I86">
-        <v>152.62200000000001</v>
+        <v>152.624</v>
       </c>
       <c r="J86">
         <v>152.584</v>
       </c>
       <c r="K86">
-        <v>152.89599999999999</v>
+        <v>152.899</v>
       </c>
       <c r="L86" s="1"/>
       <c r="M86" s="1" t="str">
@@ -10274,22 +10314,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S86" s="1"/>
-      <c r="T86" s="2">
+      <c r="S86" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U86" s="3">
+      <c r="T86" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A87">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C87" t="s">
         <v>4</v>
@@ -10298,25 +10337,25 @@
         <v>103</v>
       </c>
       <c r="E87">
-        <v>152.72800000000001</v>
+        <v>152.74600000000001</v>
       </c>
       <c r="F87">
-        <v>152.84</v>
+        <v>152.83500000000001</v>
       </c>
       <c r="G87">
-        <v>152.881</v>
+        <v>152.88</v>
       </c>
       <c r="H87">
-        <v>153.136</v>
+        <v>153.13300000000001</v>
       </c>
       <c r="I87">
-        <v>152.62299999999999</v>
+        <v>152.624</v>
       </c>
       <c r="J87">
         <v>152.584</v>
       </c>
       <c r="K87">
-        <v>152.898</v>
+        <v>152.90100000000001</v>
       </c>
       <c r="L87" s="1"/>
       <c r="M87" s="1" t="str">
@@ -10343,22 +10382,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S87" s="1"/>
-      <c r="T87" s="2">
+      <c r="S87" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U87" s="3">
+      <c r="T87" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A88">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C88" t="s">
         <v>4</v>
@@ -10367,25 +10405,25 @@
         <v>103</v>
       </c>
       <c r="E88">
-        <v>152.72900000000001</v>
+        <v>152.74199999999999</v>
       </c>
       <c r="F88">
-        <v>152.83699999999999</v>
+        <v>152.83199999999999</v>
       </c>
       <c r="G88">
-        <v>152.88</v>
+        <v>152.87899999999999</v>
       </c>
       <c r="H88">
-        <v>153.13499999999999</v>
+        <v>153.13200000000001</v>
       </c>
       <c r="I88">
-        <v>152.624</v>
+        <v>152.625</v>
       </c>
       <c r="J88">
-        <v>152.584</v>
+        <v>152.583</v>
       </c>
       <c r="K88">
-        <v>152.899</v>
+        <v>152.90199999999999</v>
       </c>
       <c r="L88" s="1"/>
       <c r="M88" s="1" t="str">
@@ -10412,22 +10450,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S88" s="1"/>
-      <c r="T88" s="2">
+      <c r="S88" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U88" s="3">
+      <c r="T88" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A89">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C89" t="s">
         <v>4</v>
@@ -10436,25 +10473,25 @@
         <v>103</v>
       </c>
       <c r="E89">
-        <v>152.74600000000001</v>
+        <v>152.70599999999999</v>
       </c>
       <c r="F89">
-        <v>152.83500000000001</v>
+        <v>152.83000000000001</v>
       </c>
       <c r="G89">
-        <v>152.88</v>
+        <v>152.87899999999999</v>
       </c>
       <c r="H89">
-        <v>153.13300000000001</v>
+        <v>153.13</v>
       </c>
       <c r="I89">
-        <v>152.624</v>
+        <v>152.626</v>
       </c>
       <c r="J89">
-        <v>152.584</v>
+        <v>152.583</v>
       </c>
       <c r="K89">
-        <v>152.90100000000001</v>
+        <v>152.904</v>
       </c>
       <c r="L89" s="1"/>
       <c r="M89" s="1" t="str">
@@ -10481,22 +10518,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S89" s="1"/>
-      <c r="T89" s="2">
+      <c r="S89" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U89" s="3">
+      <c r="T89" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A90">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C90" t="s">
         <v>4</v>
@@ -10505,25 +10541,25 @@
         <v>103</v>
       </c>
       <c r="E90">
-        <v>152.74199999999999</v>
+        <v>152.75700000000001</v>
       </c>
       <c r="F90">
-        <v>152.83199999999999</v>
+        <v>152.827</v>
       </c>
       <c r="G90">
         <v>152.87899999999999</v>
       </c>
       <c r="H90">
-        <v>153.13200000000001</v>
+        <v>153.12799999999999</v>
       </c>
       <c r="I90">
-        <v>152.625</v>
+        <v>152.62700000000001</v>
       </c>
       <c r="J90">
         <v>152.583</v>
       </c>
       <c r="K90">
-        <v>152.90199999999999</v>
+        <v>152.90600000000001</v>
       </c>
       <c r="L90" s="1"/>
       <c r="M90" s="1" t="str">
@@ -10550,22 +10586,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S90" s="1"/>
-      <c r="T90" s="2">
+      <c r="S90" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U90" s="3">
+      <c r="T90" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A91">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C91" t="s">
         <v>4</v>
@@ -10574,25 +10609,25 @@
         <v>103</v>
       </c>
       <c r="E91">
-        <v>152.70599999999999</v>
+        <v>152.649</v>
       </c>
       <c r="F91">
-        <v>152.83000000000001</v>
+        <v>152.82499999999999</v>
       </c>
       <c r="G91">
-        <v>152.87899999999999</v>
+        <v>152.87799999999999</v>
       </c>
       <c r="H91">
-        <v>153.13</v>
+        <v>153.12700000000001</v>
       </c>
       <c r="I91">
-        <v>152.626</v>
+        <v>152.62700000000001</v>
       </c>
       <c r="J91">
         <v>152.583</v>
       </c>
       <c r="K91">
-        <v>152.904</v>
+        <v>152.90700000000001</v>
       </c>
       <c r="L91" s="1"/>
       <c r="M91" s="1" t="str">
@@ -10619,22 +10654,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S91" s="1"/>
-      <c r="T91" s="2">
+      <c r="S91" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U91" s="3">
+      <c r="T91" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A92">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C92" t="s">
         <v>4</v>
@@ -10643,25 +10677,25 @@
         <v>103</v>
       </c>
       <c r="E92">
-        <v>152.75700000000001</v>
+        <v>152.648</v>
       </c>
       <c r="F92">
-        <v>152.827</v>
+        <v>152.82300000000001</v>
       </c>
       <c r="G92">
-        <v>152.87899999999999</v>
+        <v>152.87799999999999</v>
       </c>
       <c r="H92">
-        <v>153.12799999999999</v>
+        <v>153.125</v>
       </c>
       <c r="I92">
-        <v>152.62700000000001</v>
+        <v>152.62799999999999</v>
       </c>
       <c r="J92">
-        <v>152.583</v>
+        <v>152.58199999999999</v>
       </c>
       <c r="K92">
-        <v>152.90600000000001</v>
+        <v>152.90899999999999</v>
       </c>
       <c r="L92" s="1"/>
       <c r="M92" s="1" t="str">
@@ -10688,22 +10722,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S92" s="1"/>
-      <c r="T92" s="2">
+      <c r="S92" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U92" s="3">
+      <c r="T92" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A93">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C93" t="s">
         <v>4</v>
@@ -10712,25 +10745,25 @@
         <v>103</v>
       </c>
       <c r="E93">
-        <v>152.649</v>
+        <v>152.67599999999999</v>
       </c>
       <c r="F93">
-        <v>152.82499999999999</v>
+        <v>152.82</v>
       </c>
       <c r="G93">
         <v>152.87799999999999</v>
       </c>
       <c r="H93">
-        <v>153.12700000000001</v>
+        <v>153.12299999999999</v>
       </c>
       <c r="I93">
-        <v>152.62700000000001</v>
+        <v>152.62899999999999</v>
       </c>
       <c r="J93">
-        <v>152.583</v>
+        <v>152.58199999999999</v>
       </c>
       <c r="K93">
-        <v>152.90700000000001</v>
+        <v>152.91</v>
       </c>
       <c r="L93" s="1"/>
       <c r="M93" s="1" t="str">
@@ -10757,22 +10790,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S93" s="1"/>
-      <c r="T93" s="2">
+      <c r="S93" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U93" s="3">
+      <c r="T93" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A94">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C94" t="s">
         <v>4</v>
@@ -10781,25 +10813,25 @@
         <v>103</v>
       </c>
       <c r="E94">
-        <v>152.648</v>
+        <v>152.642</v>
       </c>
       <c r="F94">
-        <v>152.82300000000001</v>
+        <v>152.81800000000001</v>
       </c>
       <c r="G94">
-        <v>152.87799999999999</v>
+        <v>152.87700000000001</v>
       </c>
       <c r="H94">
-        <v>153.125</v>
+        <v>153.12200000000001</v>
       </c>
       <c r="I94">
-        <v>152.62799999999999</v>
+        <v>152.63</v>
       </c>
       <c r="J94">
         <v>152.58199999999999</v>
       </c>
       <c r="K94">
-        <v>152.90899999999999</v>
+        <v>152.91200000000001</v>
       </c>
       <c r="L94" s="1"/>
       <c r="M94" s="1" t="str">
@@ -10826,22 +10858,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S94" s="1"/>
-      <c r="T94" s="2">
+      <c r="S94" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U94" s="3">
+      <c r="T94" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A95">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C95" t="s">
         <v>4</v>
@@ -10850,25 +10881,25 @@
         <v>103</v>
       </c>
       <c r="E95">
-        <v>152.67599999999999</v>
+        <v>152.64500000000001</v>
       </c>
       <c r="F95">
-        <v>152.82</v>
+        <v>152.815</v>
       </c>
       <c r="G95">
-        <v>152.87799999999999</v>
+        <v>152.87700000000001</v>
       </c>
       <c r="H95">
-        <v>153.12299999999999</v>
+        <v>153.12</v>
       </c>
       <c r="I95">
-        <v>152.62899999999999</v>
+        <v>152.63</v>
       </c>
       <c r="J95">
         <v>152.58199999999999</v>
       </c>
       <c r="K95">
-        <v>152.91</v>
+        <v>152.91300000000001</v>
       </c>
       <c r="L95" s="1"/>
       <c r="M95" s="1" t="str">
@@ -10895,22 +10926,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S95" s="1"/>
-      <c r="T95" s="2">
+      <c r="S95" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U95" s="3">
+      <c r="T95" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A96">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C96" t="s">
         <v>4</v>
@@ -10919,25 +10949,25 @@
         <v>103</v>
       </c>
       <c r="E96">
-        <v>152.642</v>
+        <v>152.65</v>
       </c>
       <c r="F96">
-        <v>152.81800000000001</v>
+        <v>152.81299999999999</v>
       </c>
       <c r="G96">
-        <v>152.87700000000001</v>
+        <v>152.876</v>
       </c>
       <c r="H96">
-        <v>153.12200000000001</v>
+        <v>153.11799999999999</v>
       </c>
       <c r="I96">
-        <v>152.63</v>
+        <v>152.631</v>
       </c>
       <c r="J96">
-        <v>152.58199999999999</v>
+        <v>152.58099999999999</v>
       </c>
       <c r="K96">
-        <v>152.91200000000001</v>
+        <v>152.91499999999999</v>
       </c>
       <c r="L96" s="1"/>
       <c r="M96" s="1" t="str">
@@ -10964,22 +10994,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S96" s="1"/>
-      <c r="T96" s="2">
+      <c r="S96" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U96" s="3">
+      <c r="T96" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A97">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C97" t="s">
         <v>4</v>
@@ -10988,25 +11017,25 @@
         <v>103</v>
       </c>
       <c r="E97">
-        <v>152.64500000000001</v>
+        <v>152.69999999999999</v>
       </c>
       <c r="F97">
-        <v>152.815</v>
+        <v>152.81</v>
       </c>
       <c r="G97">
-        <v>152.87700000000001</v>
+        <v>152.876</v>
       </c>
       <c r="H97">
-        <v>153.12</v>
+        <v>153.11699999999999</v>
       </c>
       <c r="I97">
-        <v>152.63</v>
+        <v>152.63200000000001</v>
       </c>
       <c r="J97">
-        <v>152.58199999999999</v>
+        <v>152.58099999999999</v>
       </c>
       <c r="K97">
-        <v>152.91300000000001</v>
+        <v>152.917</v>
       </c>
       <c r="L97" s="1"/>
       <c r="M97" s="1" t="str">
@@ -11033,22 +11062,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S97" s="1"/>
-      <c r="T97" s="2">
+      <c r="S97" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U97" s="3">
+      <c r="T97" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A98">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C98" t="s">
         <v>4</v>
@@ -11057,25 +11085,25 @@
         <v>103</v>
       </c>
       <c r="E98">
-        <v>152.65</v>
+        <v>152.72200000000001</v>
       </c>
       <c r="F98">
-        <v>152.81299999999999</v>
+        <v>152.80799999999999</v>
       </c>
       <c r="G98">
         <v>152.876</v>
       </c>
       <c r="H98">
-        <v>153.11799999999999</v>
+        <v>153.11500000000001</v>
       </c>
       <c r="I98">
-        <v>152.631</v>
+        <v>152.63300000000001</v>
       </c>
       <c r="J98">
         <v>152.58099999999999</v>
       </c>
       <c r="K98">
-        <v>152.91499999999999</v>
+        <v>152.91800000000001</v>
       </c>
       <c r="L98" s="1"/>
       <c r="M98" s="1" t="str">
@@ -11102,22 +11130,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S98" s="1"/>
-      <c r="T98" s="2">
+      <c r="S98" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U98" s="3">
+      <c r="T98" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A99">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C99" t="s">
         <v>4</v>
@@ -11126,25 +11153,25 @@
         <v>103</v>
       </c>
       <c r="E99">
-        <v>152.69999999999999</v>
+        <v>152.69200000000001</v>
       </c>
       <c r="F99">
-        <v>152.81</v>
+        <v>152.80600000000001</v>
       </c>
       <c r="G99">
-        <v>152.876</v>
+        <v>152.875</v>
       </c>
       <c r="H99">
-        <v>153.11699999999999</v>
+        <v>153.113</v>
       </c>
       <c r="I99">
-        <v>152.63200000000001</v>
+        <v>152.63399999999999</v>
       </c>
       <c r="J99">
         <v>152.58099999999999</v>
       </c>
       <c r="K99">
-        <v>152.917</v>
+        <v>152.91999999999999</v>
       </c>
       <c r="L99" s="1"/>
       <c r="M99" s="1" t="str">
@@ -11171,22 +11198,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S99" s="1"/>
-      <c r="T99" s="2">
+      <c r="S99" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U99" s="3">
+      <c r="T99" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A100">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C100" t="s">
         <v>4</v>
@@ -11195,25 +11221,25 @@
         <v>103</v>
       </c>
       <c r="E100">
-        <v>152.72200000000001</v>
+        <v>152.727</v>
       </c>
       <c r="F100">
-        <v>152.80799999999999</v>
+        <v>152.803</v>
       </c>
       <c r="G100">
-        <v>152.876</v>
+        <v>152.875</v>
       </c>
       <c r="H100">
-        <v>153.11500000000001</v>
+        <v>153.11199999999999</v>
       </c>
       <c r="I100">
-        <v>152.63300000000001</v>
+        <v>152.63399999999999</v>
       </c>
       <c r="J100">
         <v>152.58099999999999</v>
       </c>
       <c r="K100">
-        <v>152.91800000000001</v>
+        <v>152.92099999999999</v>
       </c>
       <c r="L100" s="1"/>
       <c r="M100" s="1" t="str">
@@ -11240,22 +11266,21 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S100" s="1"/>
-      <c r="T100" s="2">
+      <c r="S100" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U100" s="3">
+      <c r="T100" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A101">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C101" t="s">
         <v>4</v>
@@ -11264,25 +11289,25 @@
         <v>103</v>
       </c>
       <c r="E101">
-        <v>152.69200000000001</v>
+        <v>152.71199999999999</v>
       </c>
       <c r="F101">
-        <v>152.80600000000001</v>
+        <v>152.80099999999999</v>
       </c>
       <c r="G101">
         <v>152.875</v>
       </c>
       <c r="H101">
-        <v>153.113</v>
+        <v>153.11000000000001</v>
       </c>
       <c r="I101">
-        <v>152.63399999999999</v>
+        <v>152.63499999999999</v>
       </c>
       <c r="J101">
-        <v>152.58099999999999</v>
+        <v>152.58000000000001</v>
       </c>
       <c r="K101">
-        <v>152.91999999999999</v>
+        <v>152.923</v>
       </c>
       <c r="L101" s="1"/>
       <c r="M101" s="1" t="str">
@@ -11309,150 +11334,11 @@
         <f t="shared" si="21"/>
         <v>RES</v>
       </c>
-      <c r="S101" s="1"/>
-      <c r="T101" s="2">
+      <c r="S101" s="2">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
-      <c r="U101" s="3">
-        <f t="shared" si="23"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A102">
-        <v>98</v>
-      </c>
-      <c r="B102" t="s">
-        <v>101</v>
-      </c>
-      <c r="C102" t="s">
-        <v>4</v>
-      </c>
-      <c r="D102" t="s">
-        <v>103</v>
-      </c>
-      <c r="E102">
-        <v>152.727</v>
-      </c>
-      <c r="F102">
-        <v>152.803</v>
-      </c>
-      <c r="G102">
-        <v>152.875</v>
-      </c>
-      <c r="H102">
-        <v>153.11199999999999</v>
-      </c>
-      <c r="I102">
-        <v>152.63399999999999</v>
-      </c>
-      <c r="J102">
-        <v>152.58099999999999</v>
-      </c>
-      <c r="K102">
-        <v>152.92099999999999</v>
-      </c>
-      <c r="L102" s="1"/>
-      <c r="M102" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v>RES</v>
-      </c>
-      <c r="N102" s="1" t="str">
-        <f t="shared" si="17"/>
-        <v>RES</v>
-      </c>
-      <c r="O102" s="1" t="str">
-        <f t="shared" si="18"/>
-        <v>RES</v>
-      </c>
-      <c r="P102" s="1" t="str">
-        <f t="shared" si="19"/>
-        <v>SUP</v>
-      </c>
-      <c r="Q102" s="1" t="str">
-        <f t="shared" si="20"/>
-        <v>SUP</v>
-      </c>
-      <c r="R102" s="1" t="str">
-        <f t="shared" si="21"/>
-        <v>RES</v>
-      </c>
-      <c r="S102" s="1"/>
-      <c r="T102" s="2">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="U102" s="3">
-        <f t="shared" si="23"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103">
-        <v>99</v>
-      </c>
-      <c r="B103" t="s">
-        <v>102</v>
-      </c>
-      <c r="C103" t="s">
-        <v>4</v>
-      </c>
-      <c r="D103" t="s">
-        <v>103</v>
-      </c>
-      <c r="E103">
-        <v>152.71199999999999</v>
-      </c>
-      <c r="F103">
-        <v>152.80099999999999</v>
-      </c>
-      <c r="G103">
-        <v>152.875</v>
-      </c>
-      <c r="H103">
-        <v>153.11000000000001</v>
-      </c>
-      <c r="I103">
-        <v>152.63499999999999</v>
-      </c>
-      <c r="J103">
-        <v>152.58000000000001</v>
-      </c>
-      <c r="K103">
-        <v>152.923</v>
-      </c>
-      <c r="L103" s="1"/>
-      <c r="M103" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v>RES</v>
-      </c>
-      <c r="N103" s="1" t="str">
-        <f t="shared" si="17"/>
-        <v>RES</v>
-      </c>
-      <c r="O103" s="1" t="str">
-        <f t="shared" si="18"/>
-        <v>RES</v>
-      </c>
-      <c r="P103" s="1" t="str">
-        <f t="shared" si="19"/>
-        <v>SUP</v>
-      </c>
-      <c r="Q103" s="1" t="str">
-        <f t="shared" si="20"/>
-        <v>SUP</v>
-      </c>
-      <c r="R103" s="1" t="str">
-        <f t="shared" si="21"/>
-        <v>RES</v>
-      </c>
-      <c r="S103" s="1"/>
-      <c r="T103" s="2">
-        <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="U103" s="3">
+      <c r="T101" s="3">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
